--- a/Data/FlightPlan/FPL_12OCT26.xlsx
+++ b/Data/FlightPlan/FPL_12OCT26.xlsx
@@ -542,414 +542,414 @@
     <t>16:05</t>
   </si>
   <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>10:59</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>13:24</t>
+  </si>
+  <si>
+    <t>16:27</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>04:40</t>
+  </si>
+  <si>
+    <t>08:09</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>10:47</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>16:06</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>16:07</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>15:03</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>15:02</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>12:54</t>
+  </si>
+  <si>
+    <t>16:54</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:18</t>
+  </si>
+  <si>
+    <t>13:54</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>06:56</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>13:08</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>18:39</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>08:53</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>11:19</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>13:36</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>15:29</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
     <t>21:30</t>
   </si>
   <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>13:38</t>
+  </si>
+  <si>
+    <t>15:34</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
     <t>22:15</t>
   </si>
   <si>
     <t>00:25</t>
   </si>
   <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>10:59</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>13:24</t>
-  </si>
-  <si>
-    <t>16:27</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>04:40</t>
-  </si>
-  <si>
-    <t>08:09</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>10:47</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>16:06</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>16:07</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>15:03</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>15:02</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>12:54</t>
-  </si>
-  <si>
-    <t>16:54</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:18</t>
-  </si>
-  <si>
-    <t>13:54</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>06:56</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>13:08</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>18:39</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>08:53</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>11:19</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>13:36</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>15:29</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>08:59</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>13:38</t>
-  </si>
-  <si>
-    <t>15:34</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
     <t>VN-A636</t>
   </si>
   <si>
@@ -1529,7 +1529,7 @@
     <t>Total Record(s): 339</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 12, 2026 15:15</t>
+    <t xml:space="preserve">Generated on  Oct 12, 2026 15:30</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4275,7 +4275,7 @@
         <v>13</v>
       </c>
       <c r="B77" s="7">
-        <v>1127</v>
+        <v>517</v>
       </c>
       <c t="s" r="C77" s="7">
         <v>14</v>
@@ -4291,13 +4291,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4308,7 +4308,7 @@
         <v>13</v>
       </c>
       <c r="B78" s="7">
-        <v>1128</v>
+        <v>520</v>
       </c>
       <c t="s" r="C78" s="7">
         <v>14</v>
@@ -4321,16 +4321,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c t="s" r="H78" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4357,10 +4357,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c t="s" r="J79" s="7">
         <v>83</v>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4408,7 +4408,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c t="s" r="J81" s="7">
         <v>164</v>
@@ -4416,7 +4416,7 @@
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4443,7 +4443,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c t="s" r="J82" s="7">
         <v>79</v>
@@ -4479,27 +4479,27 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
+        <v>184</v>
+      </c>
+      <c r="F84" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G84" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H84" s="8">
+        <v>185</v>
+      </c>
+      <c t="s" r="I84" s="7">
         <v>186</v>
       </c>
-      <c r="F84" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G84" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H84" s="8">
+      <c t="s" r="J84" s="7">
         <v>187</v>
-      </c>
-      <c t="s" r="I84" s="7">
-        <v>188</v>
-      </c>
-      <c t="s" r="J84" s="7">
-        <v>189</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4514,27 +4514,27 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4561,7 +4561,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>31</v>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4598,10 +4598,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4634,7 +4634,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4664,10 +4664,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4700,27 +4700,27 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
+        <v>197</v>
+      </c>
+      <c r="F91" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G91" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H91" s="8">
+        <v>198</v>
+      </c>
+      <c t="s" r="I91" s="7">
         <v>199</v>
       </c>
-      <c r="F91" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G91" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H91" s="8">
+      <c t="s" r="J91" s="7">
         <v>200</v>
-      </c>
-      <c t="s" r="I91" s="7">
-        <v>201</v>
-      </c>
-      <c t="s" r="J91" s="7">
-        <v>202</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4735,19 +4735,19 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>127</v>
@@ -4755,7 +4755,7 @@
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4790,7 +4790,7 @@
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4817,7 +4817,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c t="s" r="J94" s="7">
         <v>92</v>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4847,10 +4847,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>36</v>
@@ -4871,22 +4871,22 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
+        <v>205</v>
+      </c>
+      <c t="s" r="H96" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I96" s="7">
         <v>207</v>
       </c>
-      <c t="s" r="H96" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I96" s="7">
-        <v>209</v>
-      </c>
       <c t="s" r="J96" s="7">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4915,31 +4915,31 @@
         <v>7615</v>
       </c>
       <c t="s" r="C98" s="7">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -4950,11 +4950,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C99" s="7">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4966,7 +4966,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>55</v>
@@ -4974,7 +4974,7 @@
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -5037,7 +5037,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5082,7 +5082,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>127</v>
@@ -5090,7 +5090,7 @@
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5117,10 +5117,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5155,7 +5155,7 @@
         <v>131</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -5188,27 +5188,27 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5243,7 +5243,7 @@
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5273,7 +5273,7 @@
         <v>148</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5306,7 +5306,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5336,10 +5336,10 @@
         <v>67</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -5372,29 +5372,29 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>56</v>
       </c>
       <c t="s" r="K113" s="7">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5427,11 +5427,11 @@
         <v>28</v>
       </c>
       <c t="s" r="K114" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5461,7 +5461,7 @@
         <v>148</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5488,13 +5488,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H116" s="8">
+        <v>234</v>
+      </c>
+      <c t="s" r="I116" s="7">
+        <v>235</v>
+      </c>
+      <c t="s" r="J116" s="7">
         <v>236</v>
-      </c>
-      <c t="s" r="I116" s="7">
-        <v>237</v>
-      </c>
-      <c t="s" r="J116" s="7">
-        <v>238</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5512,22 +5512,22 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5569,7 +5569,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c t="s" r="I119" s="7">
         <v>83</v>
@@ -5580,7 +5580,7 @@
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5595,13 +5595,13 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>30</v>
@@ -5615,7 +5615,7 @@
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5639,7 +5639,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c t="s" r="I121" s="7">
         <v>22</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5725,7 +5725,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>64</v>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5758,10 +5758,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5806,7 +5806,7 @@
         <v>93</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>86</v>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5841,7 +5841,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>125</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5879,14 +5879,14 @@
         <v>127</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c t="s" r="K129" s="7">
         <v>99</v>
       </c>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5913,7 +5913,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>132</v>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5947,16 +5947,16 @@
         <v>16</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c t="s" r="K131" s="7">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
@@ -5975,13 +5975,13 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>16</v>
@@ -5990,14 +5990,14 @@
         <v>32</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c t="s" r="K132" s="7">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6047,7 +6047,7 @@
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6074,15 +6074,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6106,7 +6106,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c t="s" r="I136" s="7">
         <v>19</v>
@@ -6130,13 +6130,13 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>16</v>
@@ -6145,7 +6145,7 @@
         <v>153</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -6178,13 +6178,13 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>16</v>
@@ -6213,19 +6213,19 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
+        <v>259</v>
+      </c>
+      <c r="F140" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G140" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H140" s="8">
+        <v>198</v>
+      </c>
+      <c t="s" r="I140" s="7">
         <v>261</v>
-      </c>
-      <c r="F140" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G140" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H140" s="8">
-        <v>200</v>
-      </c>
-      <c t="s" r="I140" s="7">
-        <v>263</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>134</v>
@@ -6246,22 +6246,22 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>264</v>
+        <v>177</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6306,15 +6306,15 @@
         <v>54</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6341,7 +6341,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>43</v>
@@ -6349,7 +6349,7 @@
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6376,7 +6376,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>75</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6423,10 +6423,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>146</v>
@@ -6449,13 +6449,13 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>16</v>
@@ -6464,7 +6464,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6514,12 +6514,12 @@
         <v>156</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6546,7 +6546,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>86</v>
@@ -6554,7 +6554,7 @@
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6578,10 +6578,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>112</v>
@@ -6589,7 +6589,7 @@
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6604,22 +6604,22 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6648,7 +6648,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c t="s" r="I154" s="7">
         <v>91</v>
@@ -6672,13 +6672,13 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>16</v>
@@ -6720,7 +6720,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6732,7 +6732,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>18</v>
@@ -6740,7 +6740,7 @@
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6764,18 +6764,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6790,13 +6790,13 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
+        <v>281</v>
+      </c>
+      <c r="F159" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G159" s="8">
         <v>284</v>
-      </c>
-      <c r="F159" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G159" s="8">
-        <v>287</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>30</v>
@@ -6805,7 +6805,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6823,7 +6823,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6835,10 +6835,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6886,12 +6886,12 @@
         <v>157</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6918,15 +6918,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6956,14 +6956,14 @@
         <v>111</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c t="s" r="K164" s="7">
         <v>125</v>
       </c>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6987,18 +6987,18 @@
         <v>93</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7013,13 +7013,13 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>93</v>
@@ -7028,7 +7028,7 @@
         <v>175</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7058,10 +7058,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7094,10 +7094,10 @@
         <v>150</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c t="s" r="K168" s="7">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7131,10 +7131,10 @@
         <v>167</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c t="s" r="K169" s="7">
-        <v>177</v>
+        <v>301</v>
       </c>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7165,17 +7165,17 @@
         <v>30</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c t="s" r="K170" s="7">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7220,12 +7220,12 @@
         <v>107</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7255,12 +7255,12 @@
         <v>119</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7284,7 +7284,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c t="s" r="I174" s="7">
         <v>122</v>
@@ -7295,7 +7295,7 @@
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7310,13 +7310,13 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>16</v>
@@ -7330,7 +7330,7 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7354,7 +7354,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c t="s" r="I176" s="7">
         <v>77</v>
@@ -7378,13 +7378,13 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>16</v>
@@ -7400,61 +7400,59 @@
       <c r="M177" s="7"/>
     </row>
     <row r="178" ht="14.25" customHeight="1">
-      <c r="A178" s="6"/>
-      <c r="B178" s="7"/>
-      <c r="C178" s="7"/>
+      <c t="s" r="A178" s="6">
+        <v>13</v>
+      </c>
+      <c r="B178" s="7">
+        <v>1128</v>
+      </c>
+      <c t="s" r="C178" s="7">
+        <v>14</v>
+      </c>
       <c r="D178" s="7"/>
-      <c r="E178" s="7"/>
-      <c r="F178" s="7"/>
-      <c r="G178" s="8"/>
-      <c r="H178" s="8"/>
-      <c r="I178" s="7"/>
-      <c r="J178" s="7"/>
+      <c t="s" r="E178" s="7">
+        <v>304</v>
+      </c>
+      <c r="F178" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G178" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H178" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I178" s="7">
+        <v>311</v>
+      </c>
+      <c t="s" r="J178" s="7">
+        <v>312</v>
+      </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c r="M178" s="7"/>
     </row>
     <row r="179" ht="14.25" customHeight="1">
-      <c t="s" r="A179" s="6">
-        <v>13</v>
-      </c>
-      <c r="B179" s="7">
-        <v>632</v>
-      </c>
-      <c t="s" r="C179" s="7">
-        <v>14</v>
-      </c>
+      <c r="A179" s="6"/>
+      <c r="B179" s="7"/>
+      <c r="C179" s="7"/>
       <c r="D179" s="7"/>
-      <c t="s" r="E179" s="7">
-        <v>313</v>
-      </c>
-      <c r="F179" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G179" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H179" s="8">
-        <v>93</v>
-      </c>
-      <c t="s" r="I179" s="7">
-        <v>307</v>
-      </c>
-      <c t="s" r="J179" s="7">
-        <v>216</v>
-      </c>
+      <c r="E179" s="7"/>
+      <c r="F179" s="7"/>
+      <c r="G179" s="8"/>
+      <c r="H179" s="8"/>
+      <c r="I179" s="7"/>
+      <c r="J179" s="7"/>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
-      <c t="s" r="M179" s="7">
-        <v>314</v>
-      </c>
+      <c r="M179" s="7"/>
     </row>
     <row r="180" ht="15" customHeight="1">
       <c t="s" r="A180" s="6">
         <v>13</v>
       </c>
-      <c t="s" r="B180" s="7">
-        <v>315</v>
+      <c r="B180" s="7">
+        <v>632</v>
       </c>
       <c t="s" r="C180" s="7">
         <v>14</v>
@@ -7467,31 +7465,29 @@
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H180" s="8">
         <v>93</v>
       </c>
-      <c t="s" r="H180" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I180" s="7">
-        <v>171</v>
+        <v>305</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>233</v>
-      </c>
-      <c t="s" r="K180" s="7">
-        <v>171</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>111</v>
+        <v>314</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c t="s" r="A181" s="6">
         <v>13</v>
       </c>
-      <c r="B181" s="7">
-        <v>274</v>
+      <c t="s" r="B181" s="7">
+        <v>315</v>
       </c>
       <c t="s" r="C181" s="7">
         <v>14</v>
@@ -7504,23 +7500,23 @@
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>295</v>
+        <v>231</v>
       </c>
       <c t="s" r="K181" s="7">
-        <v>316</v>
+        <v>171</v>
       </c>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>317</v>
+        <v>111</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7528,7 +7524,7 @@
         <v>13</v>
       </c>
       <c r="B182" s="7">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c t="s" r="C182" s="7">
         <v>14</v>
@@ -7541,23 +7537,23 @@
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H182" s="8">
         <v>54</v>
       </c>
-      <c t="s" r="H182" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I182" s="7">
-        <v>318</v>
+        <v>200</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>72</v>
+        <v>292</v>
       </c>
       <c t="s" r="K182" s="7">
-        <v>270</v>
+        <v>316</v>
       </c>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7565,7 +7561,7 @@
         <v>13</v>
       </c>
       <c r="B183" s="7">
-        <v>152</v>
+        <v>275</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
@@ -7578,27 +7574,31 @@
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>263</v>
+        <v>318</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>19</v>
-      </c>
-      <c r="K183" s="7"/>
+        <v>72</v>
+      </c>
+      <c t="s" r="K183" s="7">
+        <v>267</v>
+      </c>
       <c r="L183" s="7"/>
-      <c r="M183" s="7"/>
+      <c t="s" r="M183" s="7">
+        <v>319</v>
+      </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
       <c t="s" r="A184" s="6">
         <v>13</v>
       </c>
       <c r="B184" s="7">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c t="s" r="C184" s="7">
         <v>14</v>
@@ -7611,77 +7611,75 @@
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H184" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H184" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I184" s="7">
-        <v>320</v>
+        <v>261</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>321</v>
+        <v>19</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c r="M184" s="7"/>
     </row>
     <row r="185" ht="15" customHeight="1">
-      <c r="A185" s="6"/>
-      <c r="B185" s="7"/>
-      <c r="C185" s="7"/>
+      <c t="s" r="A185" s="6">
+        <v>13</v>
+      </c>
+      <c r="B185" s="7">
+        <v>159</v>
+      </c>
+      <c t="s" r="C185" s="7">
+        <v>14</v>
+      </c>
       <c r="D185" s="7"/>
-      <c r="E185" s="7"/>
-      <c r="F185" s="7"/>
-      <c r="G185" s="8"/>
-      <c r="H185" s="8"/>
-      <c r="I185" s="7"/>
-      <c r="J185" s="7"/>
+      <c t="s" r="E185" s="7">
+        <v>313</v>
+      </c>
+      <c r="F185" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G185" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H185" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I185" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="J185" s="7">
+        <v>321</v>
+      </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c r="M185" s="7"/>
     </row>
     <row r="186" ht="14.25" customHeight="1">
-      <c t="s" r="A186" s="6">
-        <v>13</v>
-      </c>
-      <c r="B186" s="7">
-        <v>463</v>
-      </c>
-      <c t="s" r="C186" s="7">
-        <v>14</v>
-      </c>
+      <c r="A186" s="6"/>
+      <c r="B186" s="7"/>
+      <c r="C186" s="7"/>
       <c r="D186" s="7"/>
-      <c t="s" r="E186" s="7">
-        <v>322</v>
-      </c>
-      <c r="F186" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G186" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H186" s="8">
-        <v>323</v>
-      </c>
-      <c t="s" r="I186" s="7">
-        <v>86</v>
-      </c>
-      <c t="s" r="J186" s="7">
-        <v>41</v>
-      </c>
+      <c r="E186" s="7"/>
+      <c r="F186" s="7"/>
+      <c r="G186" s="8"/>
+      <c r="H186" s="8"/>
+      <c r="I186" s="7"/>
+      <c r="J186" s="7"/>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
-      <c t="s" r="M186" s="7">
-        <v>324</v>
-      </c>
+      <c r="M186" s="7"/>
     </row>
     <row r="187" ht="14.25" customHeight="1">
       <c t="s" r="A187" s="6">
         <v>13</v>
       </c>
       <c r="B187" s="7">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c t="s" r="C187" s="7">
         <v>14</v>
@@ -7694,23 +7692,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H187" s="8">
         <v>323</v>
       </c>
-      <c t="s" r="H187" s="8">
-        <v>30</v>
-      </c>
       <c t="s" r="I187" s="7">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>147</v>
-      </c>
-      <c t="s" r="K187" s="7">
-        <v>43</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -7718,7 +7714,7 @@
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
@@ -7731,23 +7727,23 @@
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
+        <v>323</v>
+      </c>
+      <c t="s" r="H188" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H188" s="8">
-        <v>312</v>
-      </c>
       <c t="s" r="I188" s="7">
-        <v>326</v>
+        <v>127</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>327</v>
+        <v>147</v>
       </c>
       <c t="s" r="K188" s="7">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>227</v>
+        <v>325</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7755,7 +7751,7 @@
         <v>13</v>
       </c>
       <c r="B189" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c t="s" r="C189" s="7">
         <v>14</v>
@@ -7768,81 +7764,83 @@
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>312</v>
+        <v>30</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>30</v>
+        <v>310</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>227</v>
+        <v>326</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c t="s" r="K189" s="7">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>208</v>
+        <v>225</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
-      <c r="A190" s="6"/>
-      <c r="B190" s="7"/>
-      <c r="C190" s="7"/>
+      <c t="s" r="A190" s="6">
+        <v>13</v>
+      </c>
+      <c r="B190" s="7">
+        <v>438</v>
+      </c>
+      <c t="s" r="C190" s="7">
+        <v>14</v>
+      </c>
       <c r="D190" s="7"/>
-      <c r="E190" s="7"/>
-      <c r="F190" s="7"/>
-      <c r="G190" s="8"/>
-      <c r="H190" s="8"/>
-      <c r="I190" s="7"/>
-      <c r="J190" s="7"/>
-      <c r="K190" s="7"/>
+      <c t="s" r="E190" s="7">
+        <v>322</v>
+      </c>
+      <c r="F190" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G190" s="8">
+        <v>310</v>
+      </c>
+      <c t="s" r="H190" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I190" s="7">
+        <v>225</v>
+      </c>
+      <c t="s" r="J190" s="7">
+        <v>299</v>
+      </c>
+      <c t="s" r="K190" s="7">
+        <v>78</v>
+      </c>
       <c r="L190" s="7"/>
-      <c r="M190" s="7"/>
+      <c t="s" r="M190" s="7">
+        <v>206</v>
+      </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
-      <c t="s" r="A191" s="6">
-        <v>13</v>
-      </c>
-      <c r="B191" s="7">
-        <v>501</v>
-      </c>
-      <c t="s" r="C191" s="7">
-        <v>14</v>
-      </c>
+      <c r="A191" s="6"/>
+      <c r="B191" s="7"/>
+      <c r="C191" s="7"/>
       <c r="D191" s="7"/>
-      <c t="s" r="E191" s="7">
-        <v>328</v>
-      </c>
-      <c r="F191" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G191" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H191" s="8">
-        <v>93</v>
-      </c>
-      <c t="s" r="I191" s="7">
-        <v>329</v>
-      </c>
-      <c t="s" r="J191" s="7">
-        <v>141</v>
-      </c>
+      <c r="E191" s="7"/>
+      <c r="F191" s="7"/>
+      <c r="G191" s="8"/>
+      <c r="H191" s="8"/>
+      <c r="I191" s="7"/>
+      <c r="J191" s="7"/>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
-      <c t="s" r="M191" s="7">
-        <v>330</v>
-      </c>
+      <c r="M191" s="7"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
       <c t="s" r="A192" s="6">
         <v>13</v>
       </c>
       <c r="B192" s="7">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c t="s" r="C192" s="7">
         <v>14</v>
@@ -7855,21 +7853,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H192" s="8">
         <v>93</v>
       </c>
-      <c t="s" r="H192" s="8">
-        <v>30</v>
-      </c>
       <c t="s" r="I192" s="7">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>216</v>
+        <v>141</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -7877,7 +7875,7 @@
         <v>13</v>
       </c>
       <c r="B193" s="7">
-        <v>563</v>
+        <v>514</v>
       </c>
       <c t="s" r="C193" s="7">
         <v>14</v>
@@ -7890,23 +7888,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
+        <v>93</v>
+      </c>
+      <c t="s" r="H193" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H193" s="8">
-        <v>332</v>
-      </c>
       <c t="s" r="I193" s="7">
-        <v>171</v>
+        <v>305</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>162</v>
-      </c>
-      <c t="s" r="K193" s="7">
-        <v>232</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -7914,7 +7910,7 @@
         <v>13</v>
       </c>
       <c r="B194" s="7">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c t="s" r="C194" s="7">
         <v>14</v>
@@ -7927,23 +7923,23 @@
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H194" s="8">
         <v>332</v>
       </c>
-      <c t="s" r="H194" s="8">
-        <v>30</v>
-      </c>
       <c t="s" r="I194" s="7">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c t="s" r="K194" s="7">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -7951,7 +7947,7 @@
         <v>13</v>
       </c>
       <c r="B195" s="7">
-        <v>143</v>
+        <v>564</v>
       </c>
       <c t="s" r="C195" s="7">
         <v>14</v>
@@ -7964,21 +7960,23 @@
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
+        <v>332</v>
+      </c>
+      <c t="s" r="H195" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H195" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I195" s="7">
-        <v>173</v>
+        <v>70</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>31</v>
-      </c>
-      <c r="K195" s="7"/>
+        <v>56</v>
+      </c>
+      <c t="s" r="K195" s="7">
+        <v>181</v>
+      </c>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -7986,7 +7984,7 @@
         <v>13</v>
       </c>
       <c r="B196" s="7">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
@@ -7999,27 +7997,29 @@
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
-      <c r="M196" s="7"/>
+      <c t="s" r="M196" s="7">
+        <v>335</v>
+      </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
       <c t="s" r="A197" s="6">
         <v>13</v>
       </c>
       <c r="B197" s="7">
-        <v>7526</v>
+        <v>146</v>
       </c>
       <c t="s" r="C197" s="7">
         <v>14</v>
@@ -8032,16 +8032,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H197" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H197" s="8">
-        <v>236</v>
-      </c>
       <c t="s" r="I197" s="7">
-        <v>95</v>
+        <v>204</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>222</v>
+        <v>33</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -8049,10 +8049,10 @@
     </row>
     <row r="198" ht="14.25" customHeight="1">
       <c t="s" r="A198" s="6">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B198" s="7">
-        <v>7527</v>
+        <v>7526</v>
       </c>
       <c t="s" r="C198" s="7">
         <v>14</v>
@@ -8065,77 +8065,75 @@
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>236</v>
+        <v>30</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>30</v>
+        <v>234</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>336</v>
+        <v>95</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>337</v>
+        <v>220</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c r="M198" s="7"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
-      <c r="A199" s="6"/>
-      <c r="B199" s="7"/>
-      <c r="C199" s="7"/>
+      <c t="s" r="A199" s="6">
+        <v>23</v>
+      </c>
+      <c r="B199" s="7">
+        <v>7527</v>
+      </c>
+      <c t="s" r="C199" s="7">
+        <v>14</v>
+      </c>
       <c r="D199" s="7"/>
-      <c r="E199" s="7"/>
-      <c r="F199" s="7"/>
-      <c r="G199" s="8"/>
-      <c r="H199" s="8"/>
-      <c r="I199" s="7"/>
-      <c r="J199" s="7"/>
+      <c t="s" r="E199" s="7">
+        <v>328</v>
+      </c>
+      <c r="F199" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G199" s="8">
+        <v>234</v>
+      </c>
+      <c t="s" r="H199" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I199" s="7">
+        <v>336</v>
+      </c>
+      <c t="s" r="J199" s="7">
+        <v>337</v>
+      </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c r="M199" s="7"/>
     </row>
     <row r="200" ht="15" customHeight="1">
-      <c t="s" r="A200" s="6">
-        <v>13</v>
-      </c>
-      <c r="B200" s="7">
-        <v>123</v>
-      </c>
-      <c t="s" r="C200" s="7">
-        <v>14</v>
-      </c>
+      <c r="A200" s="6"/>
+      <c r="B200" s="7"/>
+      <c r="C200" s="7"/>
       <c r="D200" s="7"/>
-      <c t="s" r="E200" s="7">
-        <v>338</v>
-      </c>
-      <c r="F200" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G200" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H200" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I200" s="7">
-        <v>290</v>
-      </c>
-      <c t="s" r="J200" s="7">
-        <v>339</v>
-      </c>
+      <c r="E200" s="7"/>
+      <c r="F200" s="7"/>
+      <c r="G200" s="8"/>
+      <c r="H200" s="8"/>
+      <c r="I200" s="7"/>
+      <c r="J200" s="7"/>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
-      <c t="s" r="M200" s="7">
-        <v>340</v>
-      </c>
+      <c r="M200" s="7"/>
     </row>
     <row r="201" ht="14.25" customHeight="1">
       <c t="s" r="A201" s="6">
         <v>13</v>
       </c>
       <c r="B201" s="7">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c t="s" r="C201" s="7">
         <v>14</v>
@@ -8148,21 +8146,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>314</v>
+        <v>287</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>233</v>
+        <v>339</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8170,7 +8168,7 @@
         <v>13</v>
       </c>
       <c r="B202" s="7">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c t="s" r="C202" s="7">
         <v>14</v>
@@ -8183,21 +8181,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H202" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H202" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I202" s="7">
-        <v>341</v>
+        <v>314</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>99</v>
+        <v>231</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>269</v>
+        <v>333</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8205,7 +8203,7 @@
         <v>13</v>
       </c>
       <c r="B203" s="7">
-        <v>362</v>
+        <v>133</v>
       </c>
       <c t="s" r="C203" s="7">
         <v>14</v>
@@ -8218,21 +8216,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>297</v>
+        <v>16</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>72</v>
+        <v>341</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>174</v>
+        <v>99</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>342</v>
+        <v>266</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8240,7 +8238,7 @@
         <v>13</v>
       </c>
       <c r="B204" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c t="s" r="C204" s="7">
         <v>14</v>
@@ -8253,27 +8251,29 @@
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>297</v>
+        <v>16</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>16</v>
+        <v>294</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>343</v>
+        <v>72</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
-      <c r="M204" s="7"/>
+      <c t="s" r="M204" s="7">
+        <v>342</v>
+      </c>
     </row>
     <row r="205" ht="15" customHeight="1">
       <c t="s" r="A205" s="6">
         <v>13</v>
       </c>
       <c r="B205" s="7">
-        <v>262</v>
+        <v>363</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
@@ -8286,16 +8286,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>16</v>
+        <v>294</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>344</v>
+        <v>16</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>254</v>
+        <v>183</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8306,7 +8306,7 @@
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
@@ -8319,77 +8319,75 @@
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H206" s="8">
         <v>344</v>
       </c>
-      <c t="s" r="H206" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I206" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>347</v>
+        <v>252</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c r="M206" s="7"/>
     </row>
     <row r="207" ht="14.25" customHeight="1">
-      <c r="A207" s="6"/>
-      <c r="B207" s="7"/>
-      <c r="C207" s="7"/>
+      <c t="s" r="A207" s="6">
+        <v>13</v>
+      </c>
+      <c r="B207" s="7">
+        <v>263</v>
+      </c>
+      <c t="s" r="C207" s="7">
+        <v>14</v>
+      </c>
       <c r="D207" s="7"/>
-      <c r="E207" s="7"/>
-      <c r="F207" s="7"/>
-      <c r="G207" s="8"/>
-      <c r="H207" s="8"/>
-      <c r="I207" s="7"/>
-      <c r="J207" s="7"/>
+      <c t="s" r="E207" s="7">
+        <v>338</v>
+      </c>
+      <c r="F207" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G207" s="8">
+        <v>344</v>
+      </c>
+      <c t="s" r="H207" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I207" s="7">
+        <v>346</v>
+      </c>
+      <c t="s" r="J207" s="7">
+        <v>347</v>
+      </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c r="M207" s="7"/>
     </row>
     <row r="208" ht="14.25" customHeight="1">
-      <c t="s" r="A208" s="6">
-        <v>13</v>
-      </c>
-      <c r="B208" s="7">
-        <v>197</v>
-      </c>
-      <c t="s" r="C208" s="7">
-        <v>14</v>
-      </c>
+      <c r="A208" s="6"/>
+      <c r="B208" s="7"/>
+      <c r="C208" s="7"/>
       <c r="D208" s="7"/>
-      <c t="s" r="E208" s="7">
-        <v>348</v>
-      </c>
-      <c r="F208" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G208" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H208" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I208" s="7">
-        <v>159</v>
-      </c>
-      <c t="s" r="J208" s="7">
-        <v>191</v>
-      </c>
+      <c r="E208" s="7"/>
+      <c r="F208" s="7"/>
+      <c r="G208" s="8"/>
+      <c r="H208" s="8"/>
+      <c r="I208" s="7"/>
+      <c r="J208" s="7"/>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
-      <c t="s" r="M208" s="7">
-        <v>349</v>
-      </c>
+      <c r="M208" s="7"/>
     </row>
     <row r="209" ht="14.25" customHeight="1">
       <c t="s" r="A209" s="6">
         <v>13</v>
       </c>
       <c r="B209" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c t="s" r="C209" s="7">
         <v>14</v>
@@ -8402,21 +8400,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>350</v>
+        <v>189</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>42</v>
+        <v>349</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8424,7 +8422,7 @@
         <v>13</v>
       </c>
       <c r="B210" s="7">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c t="s" r="C210" s="7">
         <v>14</v>
@@ -8437,21 +8435,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H210" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H210" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I210" s="7">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>351</v>
+        <v>42</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8459,7 +8457,7 @@
         <v>13</v>
       </c>
       <c r="B211" s="7">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c t="s" r="C211" s="7">
         <v>14</v>
@@ -8472,77 +8470,77 @@
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>33</v>
+        <v>175</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
-      <c r="M211" s="7"/>
+      <c t="s" r="M211" s="7">
+        <v>351</v>
+      </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
-      <c r="A212" s="6"/>
-      <c r="B212" s="7"/>
-      <c r="C212" s="7"/>
+      <c t="s" r="A212" s="6">
+        <v>13</v>
+      </c>
+      <c r="B212" s="7">
+        <v>194</v>
+      </c>
+      <c t="s" r="C212" s="7">
+        <v>14</v>
+      </c>
       <c r="D212" s="7"/>
-      <c r="E212" s="7"/>
-      <c r="F212" s="7"/>
-      <c r="G212" s="8"/>
-      <c r="H212" s="8"/>
-      <c r="I212" s="7"/>
-      <c r="J212" s="7"/>
+      <c t="s" r="E212" s="7">
+        <v>348</v>
+      </c>
+      <c r="F212" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G212" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H212" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I212" s="7">
+        <v>204</v>
+      </c>
+      <c t="s" r="J212" s="7">
+        <v>33</v>
+      </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c r="M212" s="7"/>
     </row>
     <row r="213" ht="14.25" customHeight="1">
-      <c t="s" r="A213" s="6">
-        <v>13</v>
-      </c>
-      <c r="B213" s="7">
-        <v>809</v>
-      </c>
-      <c t="s" r="C213" s="7">
-        <v>14</v>
-      </c>
+      <c r="A213" s="6"/>
+      <c r="B213" s="7"/>
+      <c r="C213" s="7"/>
       <c r="D213" s="7"/>
-      <c t="s" r="E213" s="7">
-        <v>352</v>
-      </c>
-      <c r="F213" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G213" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H213" s="8">
-        <v>353</v>
-      </c>
-      <c t="s" r="I213" s="7">
-        <v>216</v>
-      </c>
-      <c t="s" r="J213" s="7">
-        <v>124</v>
-      </c>
+      <c r="E213" s="7"/>
+      <c r="F213" s="7"/>
+      <c r="G213" s="8"/>
+      <c r="H213" s="8"/>
+      <c r="I213" s="7"/>
+      <c r="J213" s="7"/>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
-      <c t="s" r="M213" s="7">
-        <v>333</v>
-      </c>
+      <c r="M213" s="7"/>
     </row>
     <row r="214" ht="14.25" customHeight="1">
       <c t="s" r="A214" s="6">
         <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
@@ -8555,21 +8553,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H214" s="8">
         <v>353</v>
       </c>
-      <c t="s" r="H214" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I214" s="7">
-        <v>354</v>
+        <v>214</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>281</v>
+        <v>124</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>355</v>
+        <v>333</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8577,7 +8575,7 @@
         <v>13</v>
       </c>
       <c r="B215" s="7">
-        <v>876</v>
+        <v>808</v>
       </c>
       <c t="s" r="C215" s="7">
         <v>14</v>
@@ -8590,27 +8588,29 @@
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>16</v>
+        <v>353</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>356</v>
+        <v>16</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>147</v>
+        <v>354</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
-      <c r="M215" s="7"/>
+      <c t="s" r="M215" s="7">
+        <v>355</v>
+      </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
       <c t="s" r="A216" s="6">
         <v>13</v>
       </c>
       <c r="B216" s="7">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c t="s" r="C216" s="7">
         <v>14</v>
@@ -8623,27 +8623,29 @@
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H216" s="8">
         <v>356</v>
       </c>
-      <c t="s" r="H216" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I216" s="7">
-        <v>301</v>
+        <v>147</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>177</v>
+        <v>297</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
-      <c r="M216" s="7"/>
+      <c t="s" r="M216" s="7">
+        <v>33</v>
+      </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
       <c t="s" r="A217" s="6">
         <v>13</v>
       </c>
       <c r="B217" s="7">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c t="s" r="C217" s="7">
         <v>14</v>
@@ -8656,16 +8658,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>16</v>
+        <v>356</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>357</v>
+        <v>16</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>358</v>
+        <v>298</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>336</v>
+        <v>301</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8673,10 +8675,10 @@
     </row>
     <row r="218" ht="14.25" customHeight="1">
       <c t="s" r="A218" s="6">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B218" s="7">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c t="s" r="C218" s="7">
         <v>14</v>
@@ -8689,77 +8691,75 @@
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H218" s="8">
         <v>357</v>
       </c>
-      <c t="s" r="H218" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I218" s="7">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c r="M218" s="7"/>
     </row>
     <row r="219" ht="14.25" customHeight="1">
-      <c r="A219" s="6"/>
-      <c r="B219" s="7"/>
-      <c r="C219" s="7"/>
+      <c t="s" r="A219" s="6">
+        <v>23</v>
+      </c>
+      <c r="B219" s="7">
+        <v>859</v>
+      </c>
+      <c t="s" r="C219" s="7">
+        <v>14</v>
+      </c>
       <c r="D219" s="7"/>
-      <c r="E219" s="7"/>
-      <c r="F219" s="7"/>
-      <c r="G219" s="8"/>
-      <c r="H219" s="8"/>
-      <c r="I219" s="7"/>
-      <c r="J219" s="7"/>
+      <c t="s" r="E219" s="7">
+        <v>352</v>
+      </c>
+      <c r="F219" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G219" s="8">
+        <v>357</v>
+      </c>
+      <c t="s" r="H219" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I219" s="7">
+        <v>359</v>
+      </c>
+      <c t="s" r="J219" s="7">
+        <v>360</v>
+      </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c r="M219" s="7"/>
     </row>
     <row r="220" ht="15" customHeight="1">
-      <c t="s" r="A220" s="6">
-        <v>13</v>
-      </c>
-      <c r="B220" s="7">
-        <v>905</v>
-      </c>
-      <c t="s" r="C220" s="7">
-        <v>14</v>
-      </c>
+      <c r="A220" s="6"/>
+      <c r="B220" s="7"/>
+      <c r="C220" s="7"/>
       <c r="D220" s="7"/>
-      <c t="s" r="E220" s="7">
-        <v>361</v>
-      </c>
-      <c r="F220" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G220" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H220" s="8">
-        <v>309</v>
-      </c>
-      <c t="s" r="I220" s="7">
-        <v>362</v>
-      </c>
-      <c t="s" r="J220" s="7">
-        <v>183</v>
-      </c>
+      <c r="E220" s="7"/>
+      <c r="F220" s="7"/>
+      <c r="G220" s="8"/>
+      <c r="H220" s="8"/>
+      <c r="I220" s="7"/>
+      <c r="J220" s="7"/>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
-      <c t="s" r="M220" s="7">
-        <v>363</v>
-      </c>
+      <c r="M220" s="7"/>
     </row>
     <row r="221" ht="14.25" customHeight="1">
       <c t="s" r="A221" s="6">
         <v>13</v>
       </c>
       <c r="B221" s="7">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c t="s" r="C221" s="7">
         <v>14</v>
@@ -8772,21 +8772,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>309</v>
+        <v>30</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>30</v>
+        <v>307</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>41</v>
+        <v>362</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>364</v>
+        <v>181</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -8794,7 +8794,7 @@
         <v>13</v>
       </c>
       <c r="B222" s="7">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c t="s" r="C222" s="7">
         <v>14</v>
@@ -8807,27 +8807,29 @@
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
+        <v>307</v>
+      </c>
+      <c t="s" r="H222" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H222" s="8">
-        <v>200</v>
-      </c>
       <c t="s" r="I222" s="7">
-        <v>326</v>
+        <v>41</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>131</v>
+        <v>364</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
-      <c r="M222" s="7"/>
+      <c t="s" r="M222" s="7">
+        <v>365</v>
+      </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
       <c t="s" r="A223" s="6">
         <v>13</v>
       </c>
       <c r="B223" s="7">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c t="s" r="C223" s="7">
         <v>14</v>
@@ -8840,16 +8842,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>30</v>
+        <v>198</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>134</v>
+        <v>326</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>255</v>
+        <v>131</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8857,10 +8859,10 @@
     </row>
     <row r="224" ht="14.25" customHeight="1">
       <c t="s" r="A224" s="6">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B224" s="7">
-        <v>982</v>
+        <v>904</v>
       </c>
       <c t="s" r="C224" s="7">
         <v>14</v>
@@ -8873,77 +8875,75 @@
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
+        <v>198</v>
+      </c>
+      <c t="s" r="H224" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H224" s="8">
-        <v>67</v>
-      </c>
       <c t="s" r="I224" s="7">
-        <v>366</v>
+        <v>134</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c r="M224" s="7"/>
     </row>
     <row r="225" ht="15" customHeight="1">
-      <c r="A225" s="6"/>
-      <c r="B225" s="7"/>
-      <c r="C225" s="7"/>
+      <c t="s" r="A225" s="6">
+        <v>23</v>
+      </c>
+      <c r="B225" s="7">
+        <v>982</v>
+      </c>
+      <c t="s" r="C225" s="7">
+        <v>14</v>
+      </c>
       <c r="D225" s="7"/>
-      <c r="E225" s="7"/>
-      <c r="F225" s="7"/>
-      <c r="G225" s="8"/>
-      <c r="H225" s="8"/>
-      <c r="I225" s="7"/>
-      <c r="J225" s="7"/>
+      <c t="s" r="E225" s="7">
+        <v>361</v>
+      </c>
+      <c r="F225" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G225" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H225" s="8">
+        <v>67</v>
+      </c>
+      <c t="s" r="I225" s="7">
+        <v>366</v>
+      </c>
+      <c t="s" r="J225" s="7">
+        <v>273</v>
+      </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c r="M225" s="7"/>
     </row>
     <row r="226" ht="14.25" customHeight="1">
-      <c t="s" r="A226" s="6">
-        <v>13</v>
-      </c>
-      <c r="B226" s="7">
-        <v>823</v>
-      </c>
-      <c t="s" r="C226" s="7">
-        <v>14</v>
-      </c>
+      <c r="A226" s="6"/>
+      <c r="B226" s="7"/>
+      <c r="C226" s="7"/>
       <c r="D226" s="7"/>
-      <c t="s" r="E226" s="7">
-        <v>367</v>
-      </c>
-      <c r="F226" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G226" s="8">
-        <v>224</v>
-      </c>
-      <c t="s" r="H226" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I226" s="7">
-        <v>368</v>
-      </c>
-      <c t="s" r="J226" s="7">
-        <v>58</v>
-      </c>
+      <c r="E226" s="7"/>
+      <c r="F226" s="7"/>
+      <c r="G226" s="8"/>
+      <c r="H226" s="8"/>
+      <c r="I226" s="7"/>
+      <c r="J226" s="7"/>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
-      <c t="s" r="M226" s="7">
-        <v>369</v>
-      </c>
+      <c r="M226" s="7"/>
     </row>
     <row r="227" ht="14.25" customHeight="1">
       <c t="s" r="A227" s="6">
         <v>13</v>
       </c>
       <c r="B227" s="7">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c t="s" r="C227" s="7">
         <v>14</v>
@@ -8956,27 +8956,29 @@
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>16</v>
+        <v>222</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>370</v>
+        <v>16</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>148</v>
+        <v>368</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
-      <c r="M227" s="7"/>
+      <c t="s" r="M227" s="7">
+        <v>369</v>
+      </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
       <c t="s" r="A228" s="6">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B228" s="7">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c t="s" r="C228" s="7">
         <v>14</v>
@@ -8989,77 +8991,75 @@
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H228" s="8">
         <v>370</v>
       </c>
-      <c t="s" r="H228" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I228" s="7">
-        <v>371</v>
+        <v>148</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>372</v>
+        <v>36</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c r="M228" s="7"/>
     </row>
     <row r="229" ht="14.25" customHeight="1">
-      <c r="A229" s="6"/>
-      <c r="B229" s="7"/>
-      <c r="C229" s="7"/>
+      <c t="s" r="A229" s="6">
+        <v>23</v>
+      </c>
+      <c r="B229" s="7">
+        <v>821</v>
+      </c>
+      <c t="s" r="C229" s="7">
+        <v>14</v>
+      </c>
       <c r="D229" s="7"/>
-      <c r="E229" s="7"/>
-      <c r="F229" s="7"/>
-      <c r="G229" s="8"/>
-      <c r="H229" s="8"/>
-      <c r="I229" s="7"/>
-      <c r="J229" s="7"/>
+      <c t="s" r="E229" s="7">
+        <v>367</v>
+      </c>
+      <c r="F229" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G229" s="8">
+        <v>370</v>
+      </c>
+      <c t="s" r="H229" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I229" s="7">
+        <v>371</v>
+      </c>
+      <c t="s" r="J229" s="7">
+        <v>372</v>
+      </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c r="M229" s="7"/>
     </row>
     <row r="230" ht="15" customHeight="1">
-      <c t="s" r="A230" s="6">
-        <v>13</v>
-      </c>
-      <c r="B230" s="7">
-        <v>961</v>
-      </c>
-      <c t="s" r="C230" s="7">
-        <v>14</v>
-      </c>
+      <c r="A230" s="6"/>
+      <c r="B230" s="7"/>
+      <c r="C230" s="7"/>
       <c r="D230" s="7"/>
-      <c t="s" r="E230" s="7">
-        <v>373</v>
-      </c>
-      <c r="F230" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G230" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H230" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I230" s="7">
-        <v>333</v>
-      </c>
-      <c t="s" r="J230" s="7">
-        <v>99</v>
-      </c>
+      <c r="E230" s="7"/>
+      <c r="F230" s="7"/>
+      <c r="G230" s="8"/>
+      <c r="H230" s="8"/>
+      <c r="I230" s="7"/>
+      <c r="J230" s="7"/>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
-      <c t="s" r="M230" s="7">
-        <v>99</v>
-      </c>
+      <c r="M230" s="7"/>
     </row>
     <row r="231" ht="14.25" customHeight="1">
       <c t="s" r="A231" s="6">
         <v>13</v>
       </c>
       <c r="B231" s="7">
-        <v>946</v>
+        <v>961</v>
       </c>
       <c t="s" r="C231" s="7">
         <v>14</v>
@@ -9072,21 +9072,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H231" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H231" s="8">
-        <v>374</v>
-      </c>
       <c t="s" r="I231" s="7">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>375</v>
+        <v>99</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9094,7 +9094,7 @@
         <v>13</v>
       </c>
       <c r="B232" s="7">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c t="s" r="C232" s="7">
         <v>14</v>
@@ -9107,27 +9107,29 @@
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H232" s="8">
         <v>374</v>
       </c>
-      <c t="s" r="H232" s="8">
-        <v>30</v>
-      </c>
       <c t="s" r="I232" s="7">
-        <v>300</v>
+        <v>72</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>167</v>
+        <v>225</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
-      <c r="M232" s="7"/>
+      <c t="s" r="M232" s="7">
+        <v>375</v>
+      </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
       <c t="s" r="A233" s="6">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B233" s="7">
-        <v>960</v>
+        <v>947</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
@@ -9140,77 +9142,75 @@
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
+        <v>374</v>
+      </c>
+      <c t="s" r="H233" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H233" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I233" s="7">
-        <v>118</v>
+        <v>297</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>83</v>
+        <v>167</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c r="M233" s="7"/>
     </row>
     <row r="234" ht="14.25" customHeight="1">
-      <c r="A234" s="6"/>
-      <c r="B234" s="7"/>
-      <c r="C234" s="7"/>
+      <c t="s" r="A234" s="6">
+        <v>23</v>
+      </c>
+      <c r="B234" s="7">
+        <v>960</v>
+      </c>
+      <c t="s" r="C234" s="7">
+        <v>14</v>
+      </c>
       <c r="D234" s="7"/>
-      <c r="E234" s="7"/>
-      <c r="F234" s="7"/>
-      <c r="G234" s="8"/>
-      <c r="H234" s="8"/>
-      <c r="I234" s="7"/>
-      <c r="J234" s="7"/>
+      <c t="s" r="E234" s="7">
+        <v>373</v>
+      </c>
+      <c r="F234" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G234" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H234" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I234" s="7">
+        <v>118</v>
+      </c>
+      <c t="s" r="J234" s="7">
+        <v>83</v>
+      </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c r="M234" s="7"/>
     </row>
     <row r="235" ht="15" customHeight="1">
-      <c t="s" r="A235" s="6">
-        <v>13</v>
-      </c>
-      <c r="B235" s="7">
-        <v>510</v>
-      </c>
-      <c t="s" r="C235" s="7">
-        <v>14</v>
-      </c>
+      <c r="A235" s="6"/>
+      <c r="B235" s="7"/>
+      <c r="C235" s="7"/>
       <c r="D235" s="7"/>
-      <c t="s" r="E235" s="7">
-        <v>376</v>
-      </c>
-      <c r="F235" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G235" s="8">
-        <v>93</v>
-      </c>
-      <c t="s" r="H235" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I235" s="7">
-        <v>114</v>
-      </c>
-      <c t="s" r="J235" s="7">
-        <v>72</v>
-      </c>
+      <c r="E235" s="7"/>
+      <c r="F235" s="7"/>
+      <c r="G235" s="8"/>
+      <c r="H235" s="8"/>
+      <c r="I235" s="7"/>
+      <c r="J235" s="7"/>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
-      <c t="s" r="M235" s="7">
-        <v>377</v>
-      </c>
+      <c r="M235" s="7"/>
     </row>
     <row r="236" ht="14.25" customHeight="1">
       <c t="s" r="A236" s="6">
         <v>13</v>
       </c>
       <c r="B236" s="7">
-        <v>145</v>
+        <v>510</v>
       </c>
       <c t="s" r="C236" s="7">
         <v>14</v>
@@ -9223,23 +9223,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
+        <v>93</v>
+      </c>
+      <c t="s" r="H236" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H236" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I236" s="7">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>327</v>
-      </c>
-      <c t="s" r="K236" s="7">
-        <v>326</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>131</v>
+        <v>377</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9247,7 +9245,7 @@
         <v>13</v>
       </c>
       <c r="B237" s="7">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
@@ -9260,81 +9258,83 @@
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>252</v>
+        <v>147</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>135</v>
+        <v>327</v>
       </c>
       <c t="s" r="K237" s="7">
-        <v>78</v>
+        <v>326</v>
       </c>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="238" ht="14.25" customHeight="1">
+      <c t="s" r="A238" s="6">
+        <v>13</v>
+      </c>
+      <c r="B238" s="7">
+        <v>150</v>
+      </c>
+      <c t="s" r="C238" s="7">
+        <v>14</v>
+      </c>
+      <c r="D238" s="7"/>
+      <c t="s" r="E238" s="7">
+        <v>376</v>
+      </c>
+      <c r="F238" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G238" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H238" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I238" s="7">
+        <v>250</v>
+      </c>
+      <c t="s" r="J238" s="7">
+        <v>135</v>
+      </c>
+      <c t="s" r="K238" s="7">
+        <v>78</v>
+      </c>
+      <c r="L238" s="7"/>
+      <c t="s" r="M238" s="7">
         <v>63</v>
       </c>
     </row>
-    <row r="238" ht="14.25" customHeight="1">
-      <c r="A238" s="6"/>
-      <c r="B238" s="7"/>
-      <c r="C238" s="7"/>
-      <c r="D238" s="7"/>
-      <c r="E238" s="7"/>
-      <c r="F238" s="7"/>
-      <c r="G238" s="8"/>
-      <c r="H238" s="8"/>
-      <c r="I238" s="7"/>
-      <c r="J238" s="7"/>
-      <c r="K238" s="7"/>
-      <c r="L238" s="7"/>
-      <c r="M238" s="7"/>
-    </row>
     <row r="239" ht="14.25" customHeight="1">
-      <c t="s" r="A239" s="6">
-        <v>13</v>
-      </c>
-      <c r="B239" s="7">
-        <v>813</v>
-      </c>
-      <c t="s" r="C239" s="7">
-        <v>14</v>
-      </c>
+      <c r="A239" s="6"/>
+      <c r="B239" s="7"/>
+      <c r="C239" s="7"/>
       <c r="D239" s="7"/>
-      <c t="s" r="E239" s="7">
-        <v>378</v>
-      </c>
-      <c r="F239" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G239" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H239" s="8">
-        <v>379</v>
-      </c>
-      <c t="s" r="I239" s="7">
-        <v>276</v>
-      </c>
-      <c t="s" r="J239" s="7">
-        <v>380</v>
-      </c>
+      <c r="E239" s="7"/>
+      <c r="F239" s="7"/>
+      <c r="G239" s="8"/>
+      <c r="H239" s="8"/>
+      <c r="I239" s="7"/>
+      <c r="J239" s="7"/>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
-      <c t="s" r="M239" s="7">
-        <v>380</v>
-      </c>
+      <c r="M239" s="7"/>
     </row>
     <row r="240" ht="15" customHeight="1">
       <c t="s" r="A240" s="6">
         <v>13</v>
       </c>
       <c r="B240" s="7">
-        <v>970</v>
+        <v>813</v>
       </c>
       <c t="s" r="C240" s="7">
         <v>14</v>
@@ -9347,21 +9347,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H240" s="8">
         <v>379</v>
       </c>
-      <c t="s" r="H240" s="8">
-        <v>93</v>
-      </c>
       <c t="s" r="I240" s="7">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9369,7 +9369,7 @@
         <v>13</v>
       </c>
       <c r="B241" s="7">
-        <v>715</v>
+        <v>970</v>
       </c>
       <c t="s" r="C241" s="7">
         <v>14</v>
@@ -9382,21 +9382,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
+        <v>379</v>
+      </c>
+      <c t="s" r="H241" s="8">
         <v>93</v>
       </c>
-      <c t="s" r="H241" s="8">
-        <v>68</v>
-      </c>
       <c t="s" r="I241" s="7">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>62</v>
+        <v>381</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>62</v>
+        <v>382</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9404,7 +9404,7 @@
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
@@ -9417,77 +9417,77 @@
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
+        <v>93</v>
+      </c>
+      <c t="s" r="H242" s="8">
         <v>68</v>
       </c>
-      <c t="s" r="H242" s="8">
-        <v>93</v>
-      </c>
       <c t="s" r="I242" s="7">
-        <v>148</v>
+        <v>267</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
-      <c r="M242" s="7"/>
+      <c t="s" r="M242" s="7">
+        <v>62</v>
+      </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
-      <c r="A243" s="6"/>
-      <c r="B243" s="7"/>
-      <c r="C243" s="7"/>
+      <c t="s" r="A243" s="6">
+        <v>13</v>
+      </c>
+      <c r="B243" s="7">
+        <v>714</v>
+      </c>
+      <c t="s" r="C243" s="7">
+        <v>14</v>
+      </c>
       <c r="D243" s="7"/>
-      <c r="E243" s="7"/>
-      <c r="F243" s="7"/>
-      <c r="G243" s="8"/>
-      <c r="H243" s="8"/>
-      <c r="I243" s="7"/>
-      <c r="J243" s="7"/>
+      <c t="s" r="E243" s="7">
+        <v>378</v>
+      </c>
+      <c r="F243" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G243" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="H243" s="8">
+        <v>93</v>
+      </c>
+      <c t="s" r="I243" s="7">
+        <v>148</v>
+      </c>
+      <c t="s" r="J243" s="7">
+        <v>133</v>
+      </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c r="M243" s="7"/>
     </row>
     <row r="244" ht="14.25" customHeight="1">
-      <c t="s" r="A244" s="6">
-        <v>13</v>
-      </c>
-      <c r="B244" s="7">
-        <v>1372</v>
-      </c>
-      <c t="s" r="C244" s="7">
-        <v>14</v>
-      </c>
+      <c r="A244" s="6"/>
+      <c r="B244" s="7"/>
+      <c r="C244" s="7"/>
       <c r="D244" s="7"/>
-      <c t="s" r="E244" s="7">
-        <v>383</v>
-      </c>
-      <c r="F244" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G244" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H244" s="8">
-        <v>384</v>
-      </c>
-      <c t="s" r="I244" s="7">
-        <v>385</v>
-      </c>
-      <c t="s" r="J244" s="7">
-        <v>188</v>
-      </c>
+      <c r="E244" s="7"/>
+      <c r="F244" s="7"/>
+      <c r="G244" s="8"/>
+      <c r="H244" s="8"/>
+      <c r="I244" s="7"/>
+      <c r="J244" s="7"/>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
-      <c t="s" r="M244" s="7">
-        <v>53</v>
-      </c>
+      <c r="M244" s="7"/>
     </row>
     <row r="245" ht="15" customHeight="1">
       <c t="s" r="A245" s="6">
         <v>13</v>
       </c>
       <c r="B245" s="7">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c t="s" r="C245" s="7">
         <v>14</v>
@@ -9500,21 +9500,21 @@
         <v>320</v>
       </c>
       <c t="s" r="G245" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H245" s="8">
         <v>384</v>
       </c>
-      <c t="s" r="H245" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I245" s="7">
-        <v>276</v>
+        <v>385</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>37</v>
+        <v>186</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>386</v>
+        <v>53</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9522,7 +9522,7 @@
         <v>13</v>
       </c>
       <c r="B246" s="7">
-        <v>337</v>
+        <v>1373</v>
       </c>
       <c t="s" r="C246" s="7">
         <v>14</v>
@@ -9535,21 +9535,21 @@
         <v>320</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>16</v>
+        <v>384</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>142</v>
+        <v>273</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>273</v>
+        <v>37</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>163</v>
+        <v>386</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9557,7 +9557,7 @@
         <v>13</v>
       </c>
       <c r="B247" s="7">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c t="s" r="C247" s="7">
         <v>14</v>
@@ -9570,21 +9570,21 @@
         <v>320</v>
       </c>
       <c t="s" r="G247" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H247" s="8">
         <v>68</v>
       </c>
-      <c t="s" r="H247" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I247" s="7">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>354</v>
+        <v>270</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>387</v>
+        <v>163</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9592,7 +9592,7 @@
         <v>13</v>
       </c>
       <c r="B248" s="7">
-        <v>374</v>
+        <v>324</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
@@ -9605,21 +9605,21 @@
         <v>320</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>384</v>
+        <v>16</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>58</v>
+        <v>231</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>298</v>
+        <v>354</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>249</v>
+        <v>387</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9627,7 +9627,7 @@
         <v>13</v>
       </c>
       <c r="B249" s="7">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c t="s" r="C249" s="7">
         <v>14</v>
@@ -9640,21 +9640,21 @@
         <v>320</v>
       </c>
       <c t="s" r="G249" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H249" s="8">
         <v>384</v>
       </c>
-      <c t="s" r="H249" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I249" s="7">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>176</v>
+        <v>295</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>335</v>
+        <v>247</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9662,7 +9662,7 @@
         <v>13</v>
       </c>
       <c r="B250" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c t="s" r="C250" s="7">
         <v>14</v>
@@ -9675,27 +9675,29 @@
         <v>320</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>16</v>
+        <v>384</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>384</v>
+        <v>16</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>346</v>
+        <v>176</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
-      <c r="M250" s="7"/>
+      <c t="s" r="M250" s="7">
+        <v>335</v>
+      </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
       <c t="s" r="A251" s="6">
         <v>13</v>
       </c>
       <c r="B251" s="7">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c t="s" r="C251" s="7">
         <v>14</v>
@@ -9708,77 +9710,75 @@
         <v>320</v>
       </c>
       <c t="s" r="G251" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H251" s="8">
         <v>384</v>
       </c>
-      <c t="s" r="H251" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I251" s="7">
-        <v>388</v>
+        <v>32</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>64</v>
+        <v>346</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c r="M251" s="7"/>
     </row>
     <row r="252" ht="14.25" customHeight="1">
-      <c r="A252" s="6"/>
-      <c r="B252" s="7"/>
-      <c r="C252" s="7"/>
+      <c t="s" r="A252" s="6">
+        <v>13</v>
+      </c>
+      <c r="B252" s="7">
+        <v>377</v>
+      </c>
+      <c t="s" r="C252" s="7">
+        <v>14</v>
+      </c>
       <c r="D252" s="7"/>
-      <c r="E252" s="7"/>
-      <c r="F252" s="7"/>
-      <c r="G252" s="8"/>
-      <c r="H252" s="8"/>
-      <c r="I252" s="7"/>
-      <c r="J252" s="7"/>
+      <c t="s" r="E252" s="7">
+        <v>383</v>
+      </c>
+      <c r="F252" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G252" s="8">
+        <v>384</v>
+      </c>
+      <c t="s" r="H252" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I252" s="7">
+        <v>388</v>
+      </c>
+      <c t="s" r="J252" s="7">
+        <v>64</v>
+      </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c r="M252" s="7"/>
     </row>
     <row r="253" ht="14.25" customHeight="1">
-      <c t="s" r="A253" s="6">
-        <v>13</v>
-      </c>
-      <c r="B253" s="7">
-        <v>503</v>
-      </c>
-      <c t="s" r="C253" s="7">
-        <v>14</v>
-      </c>
+      <c r="A253" s="6"/>
+      <c r="B253" s="7"/>
+      <c r="C253" s="7"/>
       <c r="D253" s="7"/>
-      <c t="s" r="E253" s="7">
-        <v>389</v>
-      </c>
-      <c r="F253" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G253" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H253" s="8">
-        <v>93</v>
-      </c>
-      <c t="s" r="I253" s="7">
-        <v>307</v>
-      </c>
-      <c t="s" r="J253" s="7">
-        <v>216</v>
-      </c>
+      <c r="E253" s="7"/>
+      <c r="F253" s="7"/>
+      <c r="G253" s="8"/>
+      <c r="H253" s="8"/>
+      <c r="I253" s="7"/>
+      <c r="J253" s="7"/>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
-      <c t="s" r="M253" s="7">
-        <v>248</v>
-      </c>
+      <c r="M253" s="7"/>
     </row>
     <row r="254" ht="14.25" customHeight="1">
       <c t="s" r="A254" s="6">
         <v>13</v>
       </c>
       <c r="B254" s="7">
-        <v>524</v>
+        <v>503</v>
       </c>
       <c t="s" r="C254" s="7">
         <v>14</v>
@@ -9791,21 +9791,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H254" s="8">
         <v>93</v>
       </c>
-      <c t="s" r="H254" s="8">
-        <v>30</v>
-      </c>
       <c t="s" r="I254" s="7">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>390</v>
+        <v>246</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -9813,7 +9813,7 @@
         <v>13</v>
       </c>
       <c r="B255" s="7">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c t="s" r="C255" s="7">
         <v>14</v>
@@ -9826,21 +9826,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
+        <v>93</v>
+      </c>
+      <c t="s" r="H255" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H255" s="8">
-        <v>93</v>
-      </c>
       <c t="s" r="I255" s="7">
-        <v>70</v>
+        <v>282</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>41</v>
+        <v>162</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -9848,7 +9848,7 @@
         <v>13</v>
       </c>
       <c r="B256" s="7">
-        <v>703</v>
+        <v>507</v>
       </c>
       <c t="s" r="C256" s="7">
         <v>14</v>
@@ -9861,21 +9861,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H256" s="8">
         <v>93</v>
       </c>
-      <c t="s" r="H256" s="8">
-        <v>323</v>
-      </c>
       <c t="s" r="I256" s="7">
-        <v>286</v>
+        <v>70</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>251</v>
+        <v>41</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -9883,7 +9883,7 @@
         <v>13</v>
       </c>
       <c r="B257" s="7">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c t="s" r="C257" s="7">
         <v>14</v>
@@ -9896,77 +9896,77 @@
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
+        <v>93</v>
+      </c>
+      <c t="s" r="H257" s="8">
         <v>323</v>
       </c>
-      <c t="s" r="H257" s="8">
-        <v>93</v>
-      </c>
       <c t="s" r="I257" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
-      <c r="M257" s="7"/>
+      <c t="s" r="M257" s="7">
+        <v>392</v>
+      </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
-      <c r="A258" s="6"/>
-      <c r="B258" s="7"/>
-      <c r="C258" s="7"/>
+      <c t="s" r="A258" s="6">
+        <v>13</v>
+      </c>
+      <c r="B258" s="7">
+        <v>704</v>
+      </c>
+      <c t="s" r="C258" s="7">
+        <v>14</v>
+      </c>
       <c r="D258" s="7"/>
-      <c r="E258" s="7"/>
-      <c r="F258" s="7"/>
-      <c r="G258" s="8"/>
-      <c r="H258" s="8"/>
-      <c r="I258" s="7"/>
-      <c r="J258" s="7"/>
+      <c t="s" r="E258" s="7">
+        <v>389</v>
+      </c>
+      <c r="F258" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G258" s="8">
+        <v>323</v>
+      </c>
+      <c t="s" r="H258" s="8">
+        <v>93</v>
+      </c>
+      <c t="s" r="I258" s="7">
+        <v>279</v>
+      </c>
+      <c t="s" r="J258" s="7">
+        <v>204</v>
+      </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c r="M258" s="7"/>
     </row>
     <row r="259" ht="14.25" customHeight="1">
-      <c t="s" r="A259" s="6">
-        <v>13</v>
-      </c>
-      <c r="B259" s="7">
-        <v>719</v>
-      </c>
-      <c t="s" r="C259" s="7">
-        <v>14</v>
-      </c>
+      <c r="A259" s="6"/>
+      <c r="B259" s="7"/>
+      <c r="C259" s="7"/>
       <c r="D259" s="7"/>
-      <c t="s" r="E259" s="7">
-        <v>393</v>
-      </c>
-      <c r="F259" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G259" s="8">
-        <v>93</v>
-      </c>
-      <c t="s" r="H259" s="8">
-        <v>68</v>
-      </c>
-      <c t="s" r="I259" s="7">
-        <v>394</v>
-      </c>
-      <c t="s" r="J259" s="7">
-        <v>248</v>
-      </c>
+      <c r="E259" s="7"/>
+      <c r="F259" s="7"/>
+      <c r="G259" s="8"/>
+      <c r="H259" s="8"/>
+      <c r="I259" s="7"/>
+      <c r="J259" s="7"/>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
-      <c t="s" r="M259" s="7">
-        <v>395</v>
-      </c>
+      <c r="M259" s="7"/>
     </row>
     <row r="260" ht="15" customHeight="1">
       <c t="s" r="A260" s="6">
         <v>13</v>
       </c>
       <c r="B260" s="7">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c t="s" r="C260" s="7">
         <v>14</v>
@@ -9979,21 +9979,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
+        <v>93</v>
+      </c>
+      <c t="s" r="H260" s="8">
         <v>68</v>
       </c>
-      <c t="s" r="H260" s="8">
-        <v>93</v>
-      </c>
       <c t="s" r="I260" s="7">
-        <v>40</v>
+        <v>394</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>293</v>
+        <v>246</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10001,7 +10001,7 @@
         <v>13</v>
       </c>
       <c r="B261" s="7">
-        <v>973</v>
+        <v>718</v>
       </c>
       <c t="s" r="C261" s="7">
         <v>14</v>
@@ -10014,21 +10014,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="H261" s="8">
         <v>93</v>
       </c>
-      <c t="s" r="H261" s="8">
-        <v>379</v>
-      </c>
       <c t="s" r="I261" s="7">
-        <v>381</v>
+        <v>40</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>185</v>
+        <v>290</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10036,7 +10036,7 @@
         <v>13</v>
       </c>
       <c r="B262" s="7">
-        <v>814</v>
+        <v>973</v>
       </c>
       <c t="s" r="C262" s="7">
         <v>14</v>
@@ -10049,27 +10049,29 @@
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
+        <v>93</v>
+      </c>
+      <c t="s" r="H262" s="8">
         <v>379</v>
       </c>
-      <c t="s" r="H262" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I262" s="7">
-        <v>252</v>
+        <v>381</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>33</v>
+        <v>183</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
-      <c r="M262" s="7"/>
+      <c t="s" r="M262" s="7">
+        <v>397</v>
+      </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
       <c t="s" r="A263" s="6">
         <v>13</v>
       </c>
       <c r="B263" s="7">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c t="s" r="C263" s="7">
         <v>14</v>
@@ -10082,77 +10084,75 @@
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>16</v>
+        <v>379</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>224</v>
+        <v>16</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>49</v>
+        <v>250</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c r="M263" s="7"/>
     </row>
     <row r="264" ht="14.25" customHeight="1">
-      <c r="A264" s="6"/>
-      <c r="B264" s="7"/>
-      <c r="C264" s="7"/>
+      <c t="s" r="A264" s="6">
+        <v>13</v>
+      </c>
+      <c r="B264" s="7">
+        <v>822</v>
+      </c>
+      <c t="s" r="C264" s="7">
+        <v>14</v>
+      </c>
       <c r="D264" s="7"/>
-      <c r="E264" s="7"/>
-      <c r="F264" s="7"/>
-      <c r="G264" s="8"/>
-      <c r="H264" s="8"/>
-      <c r="I264" s="7"/>
-      <c r="J264" s="7"/>
+      <c t="s" r="E264" s="7">
+        <v>393</v>
+      </c>
+      <c r="F264" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G264" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H264" s="8">
+        <v>222</v>
+      </c>
+      <c t="s" r="I264" s="7">
+        <v>49</v>
+      </c>
+      <c t="s" r="J264" s="7">
+        <v>83</v>
+      </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c r="M264" s="7"/>
     </row>
     <row r="265" ht="15" customHeight="1">
-      <c t="s" r="A265" s="6">
-        <v>13</v>
-      </c>
-      <c r="B265" s="7">
-        <v>447</v>
-      </c>
-      <c t="s" r="C265" s="7">
-        <v>14</v>
-      </c>
+      <c r="A265" s="6"/>
+      <c r="B265" s="7"/>
+      <c r="C265" s="7"/>
       <c r="D265" s="7"/>
-      <c t="s" r="E265" s="7">
-        <v>398</v>
-      </c>
-      <c r="F265" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G265" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H265" s="8">
-        <v>68</v>
-      </c>
-      <c t="s" r="I265" s="7">
-        <v>98</v>
-      </c>
-      <c t="s" r="J265" s="7">
-        <v>233</v>
-      </c>
+      <c r="E265" s="7"/>
+      <c r="F265" s="7"/>
+      <c r="G265" s="8"/>
+      <c r="H265" s="8"/>
+      <c r="I265" s="7"/>
+      <c r="J265" s="7"/>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
-      <c t="s" r="M265" s="7">
-        <v>267</v>
-      </c>
+      <c r="M265" s="7"/>
     </row>
     <row r="266" ht="14.25" customHeight="1">
       <c t="s" r="A266" s="6">
         <v>13</v>
       </c>
       <c r="B266" s="7">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c t="s" r="C266" s="7">
         <v>14</v>
@@ -10165,21 +10165,21 @@
         <v>320</v>
       </c>
       <c t="s" r="G266" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H266" s="8">
         <v>68</v>
       </c>
-      <c t="s" r="H266" s="8">
-        <v>30</v>
-      </c>
       <c t="s" r="I266" s="7">
-        <v>341</v>
+        <v>98</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>43</v>
+        <v>231</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>100</v>
+        <v>264</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10187,7 +10187,7 @@
         <v>13</v>
       </c>
       <c r="B267" s="7">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c t="s" r="C267" s="7">
         <v>14</v>
@@ -10200,21 +10200,21 @@
         <v>320</v>
       </c>
       <c t="s" r="G267" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="H267" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H267" s="8">
-        <v>297</v>
-      </c>
       <c t="s" r="I267" s="7">
-        <v>184</v>
+        <v>341</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>175</v>
+        <v>43</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>399</v>
+        <v>100</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10222,7 +10222,7 @@
         <v>13</v>
       </c>
       <c r="B268" s="7">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c t="s" r="C268" s="7">
         <v>14</v>
@@ -10235,27 +10235,29 @@
         <v>320</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>297</v>
+        <v>30</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>30</v>
+        <v>294</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>75</v>
+        <v>182</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
-      <c r="M268" s="7"/>
+      <c t="s" r="M268" s="7">
+        <v>399</v>
+      </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
       <c t="s" r="A269" s="6">
         <v>13</v>
       </c>
       <c r="B269" s="7">
-        <v>7712</v>
+        <v>408</v>
       </c>
       <c t="s" r="C269" s="7">
         <v>14</v>
@@ -10268,16 +10270,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G269" s="8">
+        <v>294</v>
+      </c>
+      <c t="s" r="H269" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H269" s="8">
-        <v>400</v>
-      </c>
       <c t="s" r="I269" s="7">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>401</v>
+        <v>166</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -10285,10 +10287,10 @@
     </row>
     <row r="270" ht="15" customHeight="1">
       <c t="s" r="A270" s="6">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B270" s="7">
-        <v>7713</v>
+        <v>7712</v>
       </c>
       <c t="s" r="C270" s="7">
         <v>14</v>
@@ -10301,77 +10303,75 @@
         <v>320</v>
       </c>
       <c t="s" r="G270" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H270" s="8">
         <v>400</v>
       </c>
-      <c t="s" r="H270" s="8">
-        <v>30</v>
-      </c>
       <c t="s" r="I270" s="7">
-        <v>246</v>
+        <v>177</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c r="M270" s="7"/>
     </row>
     <row r="271" ht="14.25" customHeight="1">
-      <c r="A271" s="6"/>
-      <c r="B271" s="7"/>
-      <c r="C271" s="7"/>
+      <c t="s" r="A271" s="6">
+        <v>23</v>
+      </c>
+      <c r="B271" s="7">
+        <v>7713</v>
+      </c>
+      <c t="s" r="C271" s="7">
+        <v>14</v>
+      </c>
       <c r="D271" s="7"/>
-      <c r="E271" s="7"/>
-      <c r="F271" s="7"/>
-      <c r="G271" s="8"/>
-      <c r="H271" s="8"/>
-      <c r="I271" s="7"/>
-      <c r="J271" s="7"/>
+      <c t="s" r="E271" s="7">
+        <v>398</v>
+      </c>
+      <c r="F271" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G271" s="8">
+        <v>400</v>
+      </c>
+      <c t="s" r="H271" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I271" s="7">
+        <v>244</v>
+      </c>
+      <c t="s" r="J271" s="7">
+        <v>402</v>
+      </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c r="M271" s="7"/>
     </row>
     <row r="272" ht="14.25" customHeight="1">
-      <c t="s" r="A272" s="6">
-        <v>13</v>
-      </c>
-      <c r="B272" s="7">
-        <v>461</v>
-      </c>
-      <c t="s" r="C272" s="7">
-        <v>14</v>
-      </c>
+      <c r="A272" s="6"/>
+      <c r="B272" s="7"/>
+      <c r="C272" s="7"/>
       <c r="D272" s="7"/>
-      <c t="s" r="E272" s="7">
-        <v>403</v>
-      </c>
-      <c r="F272" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G272" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H272" s="8">
-        <v>323</v>
-      </c>
-      <c t="s" r="I272" s="7">
-        <v>53</v>
-      </c>
-      <c t="s" r="J272" s="7">
-        <v>368</v>
-      </c>
+      <c r="E272" s="7"/>
+      <c r="F272" s="7"/>
+      <c r="G272" s="8"/>
+      <c r="H272" s="8"/>
+      <c r="I272" s="7"/>
+      <c r="J272" s="7"/>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
-      <c t="s" r="M272" s="7">
-        <v>404</v>
-      </c>
+      <c r="M272" s="7"/>
     </row>
     <row r="273" ht="14.25" customHeight="1">
       <c t="s" r="A273" s="6">
         <v>13</v>
       </c>
       <c r="B273" s="7">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c t="s" r="C273" s="7">
         <v>14</v>
@@ -10384,21 +10384,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H273" s="8">
         <v>323</v>
       </c>
-      <c t="s" r="H273" s="8">
-        <v>30</v>
-      </c>
       <c t="s" r="I273" s="7">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>27</v>
+        <v>368</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10406,7 +10406,7 @@
         <v>13</v>
       </c>
       <c r="B274" s="7">
-        <v>515</v>
+        <v>462</v>
       </c>
       <c t="s" r="C274" s="7">
         <v>14</v>
@@ -10419,21 +10419,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
+        <v>323</v>
+      </c>
+      <c t="s" r="H274" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H274" s="8">
-        <v>93</v>
-      </c>
       <c t="s" r="I274" s="7">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>269</v>
+        <v>405</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10441,7 +10441,7 @@
         <v>13</v>
       </c>
       <c r="B275" s="7">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c t="s" r="C275" s="7">
         <v>14</v>
@@ -10454,21 +10454,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H275" s="8">
         <v>93</v>
       </c>
-      <c t="s" r="H275" s="8">
-        <v>30</v>
-      </c>
       <c t="s" r="I275" s="7">
-        <v>270</v>
+        <v>125</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>174</v>
+        <v>99</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>343</v>
+        <v>266</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10476,7 +10476,7 @@
         <v>13</v>
       </c>
       <c r="B276" s="7">
-        <v>773</v>
+        <v>508</v>
       </c>
       <c t="s" r="C276" s="7">
         <v>14</v>
@@ -10489,81 +10489,81 @@
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
+        <v>93</v>
+      </c>
+      <c t="s" r="H276" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H276" s="8">
-        <v>52</v>
-      </c>
       <c t="s" r="I276" s="7">
-        <v>176</v>
+        <v>267</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>252</v>
-      </c>
-      <c t="s" r="K276" s="7">
-        <v>75</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="277" ht="14.25" customHeight="1">
+      <c t="s" r="A277" s="6">
+        <v>13</v>
+      </c>
+      <c r="B277" s="7">
+        <v>773</v>
+      </c>
+      <c t="s" r="C277" s="7">
+        <v>14</v>
+      </c>
+      <c r="D277" s="7"/>
+      <c t="s" r="E277" s="7">
+        <v>403</v>
+      </c>
+      <c r="F277" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G277" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H277" s="8">
+        <v>52</v>
+      </c>
+      <c t="s" r="I277" s="7">
+        <v>176</v>
+      </c>
+      <c t="s" r="J277" s="7">
+        <v>250</v>
+      </c>
+      <c t="s" r="K277" s="7">
+        <v>75</v>
+      </c>
+      <c r="L277" s="7"/>
+      <c t="s" r="M277" s="7">
         <v>166</v>
       </c>
     </row>
-    <row r="277" ht="14.25" customHeight="1">
-      <c r="A277" s="6"/>
-      <c r="B277" s="7"/>
-      <c r="C277" s="7"/>
-      <c r="D277" s="7"/>
-      <c r="E277" s="7"/>
-      <c r="F277" s="7"/>
-      <c r="G277" s="8"/>
-      <c r="H277" s="8"/>
-      <c r="I277" s="7"/>
-      <c r="J277" s="7"/>
-      <c r="K277" s="7"/>
-      <c r="L277" s="7"/>
-      <c r="M277" s="7"/>
-    </row>
     <row r="278" ht="14.25" customHeight="1">
-      <c t="s" r="A278" s="6">
-        <v>13</v>
-      </c>
-      <c r="B278" s="7">
-        <v>121</v>
-      </c>
-      <c t="s" r="C278" s="7">
-        <v>14</v>
-      </c>
+      <c r="A278" s="6"/>
+      <c r="B278" s="7"/>
+      <c r="C278" s="7"/>
       <c r="D278" s="7"/>
-      <c t="s" r="E278" s="7">
-        <v>406</v>
-      </c>
-      <c r="F278" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G278" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H278" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I278" s="7">
-        <v>50</v>
-      </c>
-      <c t="s" r="J278" s="7">
-        <v>278</v>
-      </c>
+      <c r="E278" s="7"/>
+      <c r="F278" s="7"/>
+      <c r="G278" s="8"/>
+      <c r="H278" s="8"/>
+      <c r="I278" s="7"/>
+      <c r="J278" s="7"/>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
-      <c t="s" r="M278" s="7">
-        <v>215</v>
-      </c>
+      <c r="M278" s="7"/>
     </row>
     <row r="279" ht="14.25" customHeight="1">
       <c t="s" r="A279" s="6">
         <v>13</v>
       </c>
       <c r="B279" s="7">
-        <v>321</v>
+        <v>121</v>
       </c>
       <c t="s" r="C279" s="7">
         <v>14</v>
@@ -10576,21 +10576,21 @@
         <v>320</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>216</v>
+        <v>50</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>407</v>
+        <v>275</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>202</v>
+        <v>213</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10598,7 +10598,7 @@
         <v>13</v>
       </c>
       <c r="B280" s="7">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c t="s" r="C280" s="7">
         <v>14</v>
@@ -10611,21 +10611,21 @@
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H280" s="8">
         <v>68</v>
       </c>
-      <c t="s" r="H280" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I280" s="7">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>183</v>
+        <v>407</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>27</v>
+        <v>200</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10633,7 +10633,7 @@
         <v>13</v>
       </c>
       <c r="B281" s="7">
-        <v>136</v>
+        <v>330</v>
       </c>
       <c t="s" r="C281" s="7">
         <v>14</v>
@@ -10646,21 +10646,21 @@
         <v>320</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>408</v>
+        <v>201</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>270</v>
+        <v>181</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>409</v>
+        <v>27</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10668,7 +10668,7 @@
         <v>13</v>
       </c>
       <c r="B282" s="7">
-        <v>423</v>
+        <v>136</v>
       </c>
       <c t="s" r="C282" s="7">
         <v>14</v>
@@ -10681,27 +10681,29 @@
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H282" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H282" s="8">
-        <v>187</v>
-      </c>
       <c t="s" r="I282" s="7">
-        <v>128</v>
+        <v>408</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>44</v>
+        <v>267</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
-      <c r="M282" s="7"/>
+      <c t="s" r="M282" s="7">
+        <v>409</v>
+      </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
       <c t="s" r="A283" s="6">
         <v>13</v>
       </c>
       <c r="B283" s="7">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c t="s" r="C283" s="7">
         <v>14</v>
@@ -10714,16 +10716,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>187</v>
+        <v>30</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>30</v>
+        <v>185</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>134</v>
+        <v>44</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10734,7 +10736,7 @@
         <v>13</v>
       </c>
       <c r="B284" s="7">
-        <v>519</v>
+        <v>424</v>
       </c>
       <c t="s" r="C284" s="7">
         <v>14</v>
@@ -10747,16 +10749,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
+        <v>185</v>
+      </c>
+      <c t="s" r="H284" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H284" s="8">
-        <v>93</v>
-      </c>
       <c t="s" r="I284" s="7">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10767,7 +10769,7 @@
         <v>13</v>
       </c>
       <c r="B285" s="7">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c t="s" r="C285" s="7">
         <v>14</v>
@@ -10780,77 +10782,75 @@
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H285" s="8">
         <v>93</v>
       </c>
-      <c t="s" r="H285" s="8">
-        <v>30</v>
-      </c>
       <c t="s" r="I285" s="7">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c r="M285" s="7"/>
     </row>
     <row r="286" ht="14.25" customHeight="1">
-      <c r="A286" s="6"/>
-      <c r="B286" s="7"/>
-      <c r="C286" s="7"/>
+      <c t="s" r="A286" s="6">
+        <v>13</v>
+      </c>
+      <c r="B286" s="7">
+        <v>522</v>
+      </c>
+      <c t="s" r="C286" s="7">
+        <v>14</v>
+      </c>
       <c r="D286" s="7"/>
-      <c r="E286" s="7"/>
-      <c r="F286" s="7"/>
-      <c r="G286" s="8"/>
-      <c r="H286" s="8"/>
-      <c r="I286" s="7"/>
-      <c r="J286" s="7"/>
+      <c t="s" r="E286" s="7">
+        <v>406</v>
+      </c>
+      <c r="F286" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G286" s="8">
+        <v>93</v>
+      </c>
+      <c t="s" r="H286" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I286" s="7">
+        <v>21</v>
+      </c>
+      <c t="s" r="J286" s="7">
+        <v>48</v>
+      </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c r="M286" s="7"/>
     </row>
     <row r="287" ht="14.25" customHeight="1">
-      <c t="s" r="A287" s="6">
-        <v>13</v>
-      </c>
-      <c r="B287" s="7">
-        <v>919</v>
-      </c>
-      <c t="s" r="C287" s="7">
-        <v>14</v>
-      </c>
+      <c r="A287" s="6"/>
+      <c r="B287" s="7"/>
+      <c r="C287" s="7"/>
       <c r="D287" s="7"/>
-      <c t="s" r="E287" s="7">
-        <v>410</v>
-      </c>
-      <c r="F287" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G287" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="H287" s="8">
-        <v>52</v>
-      </c>
-      <c t="s" r="I287" s="7">
-        <v>124</v>
-      </c>
-      <c t="s" r="J287" s="7">
-        <v>99</v>
-      </c>
+      <c r="E287" s="7"/>
+      <c r="F287" s="7"/>
+      <c r="G287" s="8"/>
+      <c r="H287" s="8"/>
+      <c r="I287" s="7"/>
+      <c r="J287" s="7"/>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
-      <c t="s" r="M287" s="7">
-        <v>249</v>
-      </c>
+      <c r="M287" s="7"/>
     </row>
     <row r="288" ht="14.25" customHeight="1">
       <c t="s" r="A288" s="6">
         <v>13</v>
       </c>
       <c r="B288" s="7">
-        <v>774</v>
+        <v>919</v>
       </c>
       <c t="s" r="C288" s="7">
         <v>14</v>
@@ -10863,27 +10863,29 @@
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
+        <v>67</v>
+      </c>
+      <c t="s" r="H288" s="8">
         <v>52</v>
       </c>
-      <c t="s" r="H288" s="8">
-        <v>30</v>
-      </c>
       <c t="s" r="I288" s="7">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>245</v>
+        <v>99</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
-      <c r="M288" s="7"/>
+      <c t="s" r="M288" s="7">
+        <v>247</v>
+      </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
       <c t="s" r="A289" s="6">
         <v>13</v>
       </c>
       <c r="B289" s="7">
-        <v>517</v>
+        <v>774</v>
       </c>
       <c t="s" r="C289" s="7">
         <v>14</v>
@@ -10896,16 +10898,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
+        <v>52</v>
+      </c>
+      <c t="s" r="H289" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H289" s="8">
-        <v>93</v>
-      </c>
       <c t="s" r="I289" s="7">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>19</v>
+        <v>243</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10916,7 +10918,7 @@
         <v>13</v>
       </c>
       <c r="B290" s="7">
-        <v>520</v>
+        <v>1127</v>
       </c>
       <c t="s" r="C290" s="7">
         <v>14</v>
@@ -10929,16 +10931,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>264</v>
+        <v>47</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>21</v>
+        <v>301</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10980,7 +10982,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c t="s" r="I292" s="7">
         <v>412</v>
@@ -11012,13 +11014,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>70</v>
@@ -11050,7 +11052,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>114</v>
@@ -11082,7 +11084,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>16</v>
@@ -11091,7 +11093,7 @@
         <v>326</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -11202,7 +11204,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>162</v>
@@ -11328,7 +11330,7 @@
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11355,13 +11357,13 @@
         <v>332</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>354</v>
       </c>
       <c t="s" r="K304" s="7">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
@@ -11395,7 +11397,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c t="s" r="K305" s="7">
         <v>420</v>
@@ -11462,7 +11464,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>80</v>
@@ -11507,10 +11509,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>98</v>
@@ -11539,7 +11541,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>30</v>
@@ -11548,7 +11550,7 @@
         <v>161</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11618,7 +11620,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11650,10 +11652,10 @@
         <v>158</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11686,7 +11688,7 @@
         <v>346</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>177</v>
+        <v>301</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11719,7 +11721,7 @@
         <v>428</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11831,7 +11833,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c t="s" r="I319" s="7">
         <v>122</v>
@@ -11865,7 +11867,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>30</v>
@@ -11973,7 +11975,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c t="s" r="I323" s="7">
         <v>21</v>
@@ -12003,7 +12005,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>30</v>
@@ -12057,10 +12059,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -12130,12 +12132,12 @@
         <v>70</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12233,7 +12235,7 @@
         <v>320</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -12333,7 +12335,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12368,7 +12370,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12443,11 +12445,11 @@
         <v>62</v>
       </c>
       <c t="s" r="K338" s="7">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12477,7 +12479,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c t="s" r="K339" s="7">
         <v>327</v>
@@ -12601,7 +12603,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12704,7 +12706,7 @@
         <v>458</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12781,7 +12783,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c t="s" r="I349" s="7">
         <v>70</v>
@@ -12813,13 +12815,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>175</v>
@@ -12854,14 +12856,18 @@
         <v>68</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>300</v>
-      </c>
-      <c r="K351" s="7"/>
+        <v>297</v>
+      </c>
+      <c t="s" r="K351" s="7">
+        <v>261</v>
+      </c>
       <c r="L351" s="7"/>
-      <c r="M351" s="7"/>
+      <c t="s" r="M351" s="7">
+        <v>47</v>
+      </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
       <c t="s" r="A352" s="6">
@@ -12890,11 +12896,15 @@
         <v>47</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>265</v>
-      </c>
-      <c r="K352" s="7"/>
+        <v>262</v>
+      </c>
+      <c t="s" r="K352" s="7">
+        <v>206</v>
+      </c>
       <c r="L352" s="7"/>
-      <c r="M352" s="7"/>
+      <c t="s" r="M352" s="7">
+        <v>137</v>
+      </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
       <c r="A353" s="6"/>
@@ -12967,13 +12977,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c t="s" r="I355" s="7">
         <v>132</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12997,7 +13007,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>54</v>
@@ -13059,7 +13069,7 @@
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -13086,7 +13096,7 @@
         <v>158</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>125</v>
@@ -13153,13 +13163,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c t="s" r="I361" s="7">
         <v>130</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -13183,16 +13193,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -13275,7 +13285,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -13386,7 +13396,7 @@
         <v>332</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>380</v>
@@ -13429,7 +13439,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13456,7 +13466,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>115</v>
@@ -13494,7 +13504,7 @@
         <v>326</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13524,7 +13534,7 @@
         <v>158</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>438</v>
@@ -13534,7 +13544,7 @@
       </c>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -13564,10 +13574,10 @@
         <v>19</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c t="s" r="K374" s="7">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
@@ -13651,7 +13661,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13683,7 +13693,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>175</v>
@@ -13721,7 +13731,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13751,10 +13761,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13867,7 +13877,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>133</v>
@@ -13875,7 +13885,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -13938,7 +13948,7 @@
         <v>480</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13980,7 +13990,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c t="s" r="I388" s="7">
         <v>69</v>
@@ -14012,7 +14022,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>16</v>
@@ -14050,16 +14060,16 @@
         <v>16</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>318</v>
       </c>
       <c t="s" r="K390" s="7">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
@@ -14084,7 +14094,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>16</v>
@@ -14093,7 +14103,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c t="s" r="K391" s="7">
         <v>115</v>
@@ -14133,7 +14143,7 @@
         <v>131</v>
       </c>
       <c t="s" r="K392" s="7">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
@@ -14170,7 +14180,7 @@
         <v>20</v>
       </c>
       <c t="s" r="K393" s="7">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
@@ -14222,11 +14232,11 @@
         <v>142</v>
       </c>
       <c t="s" r="K395" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14253,7 +14263,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>484</v>
@@ -14301,7 +14311,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>176</v>
@@ -14335,7 +14345,7 @@
         <v>5805</v>
       </c>
       <c t="s" r="C400" s="7">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
@@ -14370,7 +14380,7 @@
         <v>5806</v>
       </c>
       <c t="s" r="C401" s="7">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
@@ -14434,7 +14444,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>25</v>
@@ -14507,7 +14517,7 @@
         <v>148</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14588,12 +14598,12 @@
         <v>380</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>177</v>
+        <v>301</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14620,7 +14630,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>156</v>
@@ -14668,7 +14678,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>107</v>
@@ -14711,7 +14721,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -14738,7 +14748,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>501</v>
@@ -14821,7 +14831,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>504</v>

--- a/Data/FlightPlan/FPL_12OCT26.xlsx
+++ b/Data/FlightPlan/FPL_12OCT26.xlsx
@@ -143,1161 +143,1161 @@
     <t>01:30</t>
   </si>
   <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>02:45</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>VN-A203</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>17:17</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>22:58</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>VN-A500</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>12:33</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>14:52</t>
+  </si>
+  <si>
+    <t>HGH</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>20:18</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A521</t>
+  </si>
+  <si>
+    <t>PUS</t>
+  </si>
+  <si>
+    <t>PQC</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>11:27</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>14:38</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>18:16</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>20:49</t>
+  </si>
+  <si>
+    <t>VN-A522</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>09:32</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>11:48</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>16:18</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>18:44</t>
+  </si>
+  <si>
+    <t>DAD</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>20:33</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>13:42</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>17:31</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>23:31</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>07:59</t>
+  </si>
+  <si>
+    <t>09:36</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>15:23</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>VN-A530</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>10:41</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>12:51</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>15:39</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>20:41</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A532</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>09:04</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>12:11</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>18:48</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>20:51</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:36</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>10:33</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>18:12</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>20:34</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>20:04</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>19:27</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>10:59</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>18:33</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>22:31</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>13:24</t>
+  </si>
+  <si>
+    <t>16:27</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>01:12</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>04:40</t>
+  </si>
+  <si>
+    <t>08:09</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>10:47</t>
+  </si>
+  <si>
+    <t>20:59</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>01:25</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>01:19</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>16:06</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>18:07</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>16:07</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>21:32</t>
+  </si>
+  <si>
+    <t>04:00</t>
+  </si>
+  <si>
     <t>22:15</t>
   </si>
   <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>15:03</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>15:02</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>12:54</t>
+  </si>
+  <si>
+    <t>16:54</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>19:16</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>21:39</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:18</t>
+  </si>
+  <si>
+    <t>13:54</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>06:56</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>13:08</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>19:19</t>
+  </si>
+  <si>
+    <t>20:54</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>18:39</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>08:53</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>11:19</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>13:36</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>15:29</t>
+  </si>
+  <si>
+    <t>17:23</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>21:57</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>00:35</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>13:38</t>
+  </si>
+  <si>
+    <t>15:34</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>18:29</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>20:01</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>621A *</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>14:03</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>16:34</t>
+  </si>
+  <si>
+    <t>19:22</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>22:27</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>15:41</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>18:01</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>20:03</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>07:21</t>
+  </si>
+  <si>
+    <t>09:14</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>12:52</t>
+  </si>
+  <si>
+    <t>16:09</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:54</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>15:54</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>19:44</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>21:49</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>09:34</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>15:42</t>
+  </si>
+  <si>
+    <t>19:03</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>13:44</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>19:13</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:16</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>03:40</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>11:37</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>14:41</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>20:53</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>14:24</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>00:43</t>
+  </si>
+  <si>
     <t>02:00</t>
   </si>
   <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:40</t>
-  </si>
-  <si>
-    <t>VN-A203</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>12:46</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>17:17</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>22:58</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>VN-A500</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>12:33</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>14:52</t>
-  </si>
-  <si>
-    <t>HGH</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>20:18</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>00:08</t>
-  </si>
-  <si>
-    <t>VN-A521</t>
-  </si>
-  <si>
-    <t>PUS</t>
-  </si>
-  <si>
-    <t>PQC</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>11:27</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>14:38</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>18:16</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>20:49</t>
-  </si>
-  <si>
-    <t>VN-A522</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>09:32</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>11:48</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>16:18</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>18:44</t>
-  </si>
-  <si>
-    <t>DAD</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>20:33</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>13:42</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>17:31</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>23:31</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>07:59</t>
-  </si>
-  <si>
-    <t>09:36</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>12:59</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>15:23</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>VN-A530</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>10:41</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>12:51</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>15:39</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>20:41</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A532</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>09:04</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>12:11</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>18:48</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>20:51</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:36</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>10:33</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>15:48</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>18:12</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>20:34</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>22:23</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>20:04</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>19:27</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>10:59</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>18:33</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>22:31</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>13:24</t>
-  </si>
-  <si>
-    <t>16:27</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>01:12</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>08:09</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>10:47</t>
-  </si>
-  <si>
-    <t>20:59</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>01:25</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>01:19</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>16:06</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>18:07</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>16:07</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>21:32</t>
-  </si>
-  <si>
-    <t>04:00</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>15:03</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>15:02</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>12:54</t>
-  </si>
-  <si>
-    <t>16:54</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>19:16</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>21:39</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:18</t>
-  </si>
-  <si>
-    <t>13:54</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>06:56</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>13:08</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>19:19</t>
-  </si>
-  <si>
-    <t>20:54</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>18:39</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>08:53</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>11:19</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>13:36</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>15:29</t>
-  </si>
-  <si>
-    <t>17:23</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>21:57</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>00:35</t>
-  </si>
-  <si>
-    <t>02:45</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>08:59</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>13:38</t>
-  </si>
-  <si>
-    <t>15:34</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>18:29</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>20:01</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>621A *</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>14:03</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>16:34</t>
-  </si>
-  <si>
-    <t>19:22</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>22:27</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>12:53</t>
-  </si>
-  <si>
-    <t>15:41</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>18:01</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>20:03</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>07:21</t>
-  </si>
-  <si>
-    <t>09:14</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>12:52</t>
-  </si>
-  <si>
-    <t>16:09</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:54</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>15:54</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>19:44</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>21:49</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>09:34</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>15:42</t>
-  </si>
-  <si>
-    <t>19:03</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>13:44</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>19:13</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:16</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>03:40</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>11:37</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>14:41</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>20:53</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>14:24</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>00:43</t>
-  </si>
-  <si>
     <t>06:10</t>
   </si>
   <si>
@@ -1532,6 +1532,9 @@
     <t>01:15</t>
   </si>
   <si>
+    <t>01:14</t>
+  </si>
+  <si>
     <t>02:20</t>
   </si>
   <si>
@@ -1754,6 +1757,9 @@
     <t>BNE</t>
   </si>
   <si>
+    <t>06:01</t>
+  </si>
+  <si>
     <t>VN-A817</t>
   </si>
   <si>
@@ -1778,7 +1784,7 @@
     <t>Total Record(s): 340</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 12, 2026 21:00</t>
+    <t xml:space="preserve">Generated on  Oct 12, 2026 21:35</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4473,7 +4479,7 @@
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c t="s" r="M73" s="7">
-        <v>191</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -4503,7 +4509,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4515,15 +4521,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I75" s="7">
+        <v>192</v>
+      </c>
+      <c t="s" r="J75" s="7">
         <v>193</v>
-      </c>
-      <c t="s" r="J75" s="7">
-        <v>194</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4538,7 +4544,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4550,15 +4556,15 @@
         <v>110</v>
       </c>
       <c t="s" r="I76" s="7">
+        <v>194</v>
+      </c>
+      <c t="s" r="J76" s="7">
         <v>195</v>
-      </c>
-      <c t="s" r="J76" s="7">
-        <v>196</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4573,7 +4579,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4585,7 +4591,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c t="s" r="J77" s="7">
         <v>119</v>
@@ -4593,7 +4599,7 @@
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4608,7 +4614,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4630,7 +4636,7 @@
       </c>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4645,7 +4651,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4657,17 +4663,17 @@
         <v>34</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c t="s" r="J79" s="7">
         <v>21</v>
       </c>
       <c t="s" r="K79" s="7">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>191</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4682,7 +4688,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4691,10 +4697,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H80" s="8">
+        <v>202</v>
+      </c>
+      <c t="s" r="I80" s="7">
         <v>203</v>
-      </c>
-      <c t="s" r="I80" s="7">
-        <v>204</v>
       </c>
       <c t="s" r="J80" s="7">
         <v>100</v>
@@ -4730,7 +4736,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4742,7 +4748,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c t="s" r="J82" s="7">
         <v>183</v>
@@ -4750,7 +4756,7 @@
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c t="s" r="M82" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -4765,7 +4771,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4777,7 +4783,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c t="s" r="J83" s="7">
         <v>95</v>
@@ -4785,7 +4791,7 @@
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4815,27 +4821,27 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
+        <v>209</v>
+      </c>
+      <c r="F85" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G85" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H85" s="8">
         <v>210</v>
       </c>
-      <c r="F85" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G85" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H85" s="8">
+      <c t="s" r="I85" s="7">
         <v>211</v>
       </c>
-      <c t="s" r="I85" s="7">
+      <c t="s" r="J85" s="7">
         <v>212</v>
-      </c>
-      <c t="s" r="J85" s="7">
-        <v>213</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4850,27 +4856,27 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
+        <v>209</v>
+      </c>
+      <c r="F86" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G86" s="8">
         <v>210</v>
       </c>
-      <c r="F86" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G86" s="8">
-        <v>211</v>
-      </c>
       <c t="s" r="H86" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I86" s="7">
+        <v>213</v>
+      </c>
+      <c t="s" r="J86" s="7">
         <v>214</v>
-      </c>
-      <c t="s" r="J86" s="7">
-        <v>215</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4885,7 +4891,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4897,7 +4903,7 @@
         <v>99</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="J87" s="7">
         <v>35</v>
@@ -4922,7 +4928,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4934,15 +4940,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I88" s="7">
+        <v>217</v>
+      </c>
+      <c t="s" r="J88" s="7">
         <v>218</v>
-      </c>
-      <c t="s" r="J88" s="7">
-        <v>219</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4957,7 +4963,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4969,15 +4975,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I89" s="7">
+        <v>220</v>
+      </c>
+      <c t="s" r="J89" s="7">
         <v>221</v>
-      </c>
-      <c t="s" r="J89" s="7">
-        <v>222</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4992,7 +4998,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -5004,7 +5010,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>28</v>
@@ -5040,27 +5046,27 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
+        <v>224</v>
+      </c>
+      <c r="F92" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G92" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H92" s="8">
         <v>225</v>
       </c>
-      <c r="F92" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G92" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H92" s="8">
+      <c t="s" r="I92" s="7">
         <v>226</v>
       </c>
-      <c t="s" r="I92" s="7">
+      <c t="s" r="J92" s="7">
         <v>227</v>
-      </c>
-      <c t="s" r="J92" s="7">
-        <v>228</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -5075,19 +5081,19 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
+        <v>224</v>
+      </c>
+      <c r="F93" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G93" s="8">
         <v>225</v>
       </c>
-      <c r="F93" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G93" s="8">
-        <v>226</v>
-      </c>
       <c t="s" r="H93" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c t="s" r="J93" s="7">
         <v>148</v>
@@ -5095,7 +5101,7 @@
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -5110,7 +5116,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -5130,7 +5136,7 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -5145,7 +5151,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -5157,10 +5163,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I95" s="7">
+        <v>231</v>
+      </c>
+      <c t="s" r="J95" s="7">
         <v>232</v>
-      </c>
-      <c t="s" r="J95" s="7">
-        <v>233</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -5180,7 +5186,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -5189,10 +5195,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H96" s="8">
+        <v>233</v>
+      </c>
+      <c t="s" r="I96" s="7">
         <v>234</v>
-      </c>
-      <c t="s" r="I96" s="7">
-        <v>235</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>26</v>
@@ -5200,7 +5206,7 @@
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -5215,22 +5221,22 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c t="s" r="H97" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I97" s="7">
+        <v>236</v>
+      </c>
+      <c t="s" r="J97" s="7">
         <v>237</v>
-      </c>
-      <c t="s" r="J97" s="7">
-        <v>238</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -5259,26 +5265,26 @@
         <v>7615</v>
       </c>
       <c t="s" r="C99" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
+        <v>239</v>
+      </c>
+      <c r="F99" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G99" s="8">
         <v>240</v>
-      </c>
-      <c r="F99" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G99" s="8">
-        <v>241</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>49</v>
+        <v>241</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -5294,11 +5300,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C100" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5333,7 +5339,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -5345,10 +5351,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -5368,7 +5374,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5405,7 +5411,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5465,7 +5471,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c t="s" r="J105" s="7">
         <v>148</v>
@@ -5500,7 +5506,7 @@
         <v>84</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="J106" s="7">
         <v>253</v>
@@ -5585,7 +5591,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>258</v>
@@ -5593,7 +5599,7 @@
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c t="s" r="M109" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -5728,7 +5734,7 @@
         <v>264</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5783,7 +5789,7 @@
       </c>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5816,7 +5822,7 @@
         <v>32</v>
       </c>
       <c t="s" r="K116" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
@@ -5855,7 +5861,7 @@
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5882,13 +5888,13 @@
         <v>84</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>271</v>
       </c>
       <c t="s" r="K118" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
@@ -5925,11 +5931,11 @@
         <v>273</v>
       </c>
       <c t="s" r="K119" s="7">
-        <v>44</v>
+        <v>274</v>
       </c>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5959,7 +5965,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5974,12 +5980,12 @@
         <v>100</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -5994,7 +6000,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -6014,7 +6020,7 @@
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -6029,7 +6035,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -6077,7 +6083,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -6112,7 +6118,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -6124,7 +6130,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>79</v>
@@ -6132,7 +6138,7 @@
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -6147,7 +6153,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -6159,10 +6165,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -6195,7 +6201,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6207,7 +6213,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>103</v>
@@ -6230,7 +6236,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6265,7 +6271,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6280,14 +6286,14 @@
         <v>148</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="K131" s="7">
         <v>117</v>
       </c>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6302,7 +6308,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6314,13 +6320,13 @@
         <v>16</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>153</v>
       </c>
       <c t="s" r="K132" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
@@ -6339,7 +6345,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6348,16 +6354,16 @@
         <v>16</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="K133" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
@@ -6376,13 +6382,13 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>16</v>
@@ -6394,7 +6400,7 @@
         <v>271</v>
       </c>
       <c t="s" r="K134" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
@@ -6428,7 +6434,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6448,7 +6454,7 @@
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -6463,7 +6469,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6475,15 +6481,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6498,7 +6504,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6507,7 +6513,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="I138" s="7">
         <v>19</v>
@@ -6518,7 +6524,7 @@
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6533,13 +6539,13 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>16</v>
@@ -6548,7 +6554,7 @@
         <v>172</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6581,13 +6587,13 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>16</v>
@@ -6601,7 +6607,7 @@
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6616,7 +6622,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6625,10 +6631,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>154</v>
@@ -6636,7 +6642,7 @@
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6651,27 +6657,27 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6701,7 +6707,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6713,15 +6719,15 @@
         <v>68</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6736,7 +6742,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6748,7 +6754,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>55</v>
@@ -6756,7 +6762,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6771,7 +6777,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6783,7 +6789,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>91</v>
@@ -6821,7 +6827,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6830,10 +6836,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>165</v>
@@ -6856,27 +6862,27 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6906,7 +6912,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6921,12 +6927,12 @@
         <v>175</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6941,7 +6947,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6953,7 +6959,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>103</v>
@@ -6961,7 +6967,7 @@
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6976,7 +6982,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6985,10 +6991,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>134</v>
@@ -6996,7 +7002,7 @@
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -7011,22 +7017,22 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -7046,7 +7052,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -7055,7 +7061,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="I156" s="7">
         <v>108</v>
@@ -7066,7 +7072,7 @@
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -7081,13 +7087,13 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>16</v>
@@ -7101,7 +7107,7 @@
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -7131,7 +7137,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -7143,7 +7149,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>18</v>
@@ -7151,7 +7157,7 @@
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -7166,7 +7172,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7175,18 +7181,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7201,13 +7207,13 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>34</v>
@@ -7216,12 +7222,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -7236,7 +7242,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7251,7 +7257,7 @@
         <v>248</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -7284,7 +7290,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7304,7 +7310,7 @@
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7319,7 +7325,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7331,15 +7337,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7354,7 +7360,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7369,14 +7375,14 @@
         <v>133</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="K166" s="7">
         <v>146</v>
       </c>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7391,7 +7397,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7400,18 +7406,18 @@
         <v>110</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -7426,27 +7432,27 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7461,7 +7467,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7473,15 +7479,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7496,7 +7502,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7511,14 +7517,14 @@
         <v>37</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="K170" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7533,7 +7539,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7548,14 +7554,14 @@
         <v>187</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="K171" s="7">
         <v>60</v>
       </c>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7570,7 +7576,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7582,7 +7588,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>343</v>
+        <v>44</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>254</v>
@@ -7592,7 +7598,7 @@
       </c>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>345</v>
+        <v>45</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7622,7 +7628,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7637,12 +7643,12 @@
         <v>126</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7657,7 +7663,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7672,12 +7678,12 @@
         <v>141</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7692,7 +7698,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7701,7 +7707,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c t="s" r="I176" s="7">
         <v>143</v>
@@ -7712,7 +7718,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7727,13 +7733,13 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>16</v>
@@ -7747,7 +7753,7 @@
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7762,7 +7768,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7771,7 +7777,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c t="s" r="I178" s="7">
         <v>93</v>
@@ -7782,7 +7788,7 @@
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7797,19 +7803,19 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>59</v>
@@ -7817,7 +7823,7 @@
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7832,7 +7838,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7844,13 +7850,13 @@
         <v>34</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>44</v>
+        <v>274</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>356</v>
+        <v>81</v>
       </c>
       <c t="s" r="K180" s="7">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
@@ -7884,7 +7890,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7896,7 +7902,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>243</v>
@@ -7904,7 +7910,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7912,14 +7918,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B183" s="7">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7931,13 +7937,13 @@
         <v>16</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>268</v>
       </c>
       <c t="s" r="K183" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
@@ -7956,7 +7962,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7968,17 +7974,17 @@
         <v>68</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="K184" s="7">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -7993,7 +7999,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -8005,17 +8011,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>88</v>
       </c>
       <c t="s" r="K185" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -8030,7 +8036,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -8042,7 +8048,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>19</v>
@@ -8050,7 +8056,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -8065,7 +8071,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -8077,7 +8083,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>263</v>
@@ -8085,7 +8091,7 @@
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -8115,7 +8121,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8124,7 +8130,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>103</v>
@@ -8135,7 +8141,7 @@
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -8150,13 +8156,13 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>34</v>
@@ -8172,7 +8178,7 @@
       </c>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -8187,7 +8193,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8196,20 +8202,20 @@
         <v>34</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c t="s" r="K191" s="7">
         <v>35</v>
       </c>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8224,13 +8230,13 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>34</v>
@@ -8239,14 +8245,14 @@
         <v>260</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c t="s" r="K192" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8276,7 +8282,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8288,7 +8294,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>160</v>
@@ -8296,7 +8302,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -8311,7 +8317,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8323,7 +8329,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>243</v>
@@ -8331,7 +8337,7 @@
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8346,7 +8352,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8355,10 +8361,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>181</v>
@@ -8368,7 +8374,7 @@
       </c>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8383,13 +8389,13 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>34</v>
@@ -8401,11 +8407,11 @@
         <v>70</v>
       </c>
       <c t="s" r="K197" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8420,7 +8426,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8432,7 +8438,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>35</v>
@@ -8440,7 +8446,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8455,7 +8461,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8467,7 +8473,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>38</v>
@@ -8475,7 +8481,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8490,7 +8496,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8523,7 +8529,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8535,10 +8541,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -8571,7 +8577,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8583,15 +8589,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8606,7 +8612,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8618,7 +8624,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>268</v>
@@ -8626,7 +8632,7 @@
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8641,7 +8647,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8653,7 +8659,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>117</v>
@@ -8661,7 +8667,7 @@
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8676,7 +8682,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8685,18 +8691,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I206" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8711,27 +8717,27 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="H207" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8746,7 +8752,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8755,18 +8761,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8781,27 +8787,27 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8831,7 +8837,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8846,12 +8852,12 @@
         <v>178</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8866,7 +8872,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8878,10 +8884,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8901,7 +8907,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8916,12 +8922,12 @@
         <v>183</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8936,7 +8942,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8948,7 +8954,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>38</v>
@@ -8956,7 +8962,7 @@
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8986,7 +8992,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8995,7 +9001,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c t="s" r="I216" s="7">
         <v>243</v>
@@ -9006,7 +9012,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -9021,27 +9027,27 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
+        <v>400</v>
+      </c>
+      <c r="F217" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G217" s="8">
+        <v>401</v>
+      </c>
+      <c t="s" r="H217" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I217" s="7">
         <v>402</v>
       </c>
-      <c r="F217" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G217" s="8">
-        <v>403</v>
-      </c>
-      <c t="s" r="H217" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I217" s="7">
-        <v>404</v>
-      </c>
       <c t="s" r="J217" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -9056,7 +9062,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -9065,18 +9071,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c t="s" r="I218" s="7">
         <v>166</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -9091,27 +9097,27 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
+        <v>404</v>
+      </c>
+      <c t="s" r="H219" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I219" s="7">
+        <v>340</v>
+      </c>
+      <c t="s" r="J219" s="7">
         <v>406</v>
-      </c>
-      <c t="s" r="H219" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I219" s="7">
-        <v>339</v>
-      </c>
-      <c t="s" r="J219" s="7">
-        <v>408</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -9126,7 +9132,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9135,20 +9141,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c t="s" r="K220" s="7">
         <v>190</v>
       </c>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9163,29 +9169,29 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>48</v>
+        <v>411</v>
       </c>
       <c t="s" r="J221" s="7">
+        <v>412</v>
+      </c>
+      <c t="s" r="K221" s="7">
         <v>413</v>
-      </c>
-      <c t="s" r="K221" s="7">
-        <v>414</v>
       </c>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9215,7 +9221,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9224,18 +9230,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -9250,13 +9256,13 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>34</v>
@@ -9265,12 +9271,12 @@
         <v>53</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -9285,7 +9291,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9294,10 +9300,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>152</v>
@@ -9320,13 +9326,13 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>34</v>
@@ -9335,12 +9341,12 @@
         <v>154</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9355,7 +9361,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9367,10 +9373,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -9403,7 +9409,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9415,7 +9421,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>72</v>
@@ -9423,7 +9429,7 @@
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9438,7 +9444,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9447,7 +9453,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c t="s" r="I230" s="7">
         <v>167</v>
@@ -9458,7 +9464,7 @@
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9473,19 +9479,19 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>45</v>
+        <v>428</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>429</v>
@@ -9533,7 +9539,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>117</v>
@@ -9603,7 +9609,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>187</v>
@@ -9724,10 +9730,10 @@
         <v>166</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c t="s" r="K239" s="7">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
@@ -9758,13 +9764,13 @@
         <v>34</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>155</v>
       </c>
       <c t="s" r="K240" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
@@ -9810,7 +9816,7 @@
         <v>438</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>439</v>
@@ -9845,7 +9851,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>440</v>
@@ -9880,7 +9886,7 @@
         <v>84</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>76</v>
@@ -9918,7 +9924,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9968,7 +9974,7 @@
         <v>445</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -10000,7 +10006,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>27</v>
@@ -10038,7 +10044,7 @@
         <v>161</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -10073,7 +10079,7 @@
         <v>268</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -10108,12 +10114,12 @@
         <v>72</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -10143,12 +10149,12 @@
         <v>73</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -10178,7 +10184,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -10210,7 +10216,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>79</v>
@@ -10218,7 +10224,7 @@
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10260,7 +10266,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>243</v>
@@ -10268,7 +10274,7 @@
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10295,7 +10301,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J257" s="7">
         <v>181</v>
@@ -10362,13 +10368,13 @@
         <v>110</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -10394,16 +10400,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -10453,7 +10459,7 @@
         <v>454</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -10488,7 +10494,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -10523,7 +10529,7 @@
         <v>440</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -10555,7 +10561,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>38</v>
@@ -10646,7 +10652,7 @@
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10673,7 +10679,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>55</v>
@@ -10705,13 +10711,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -10737,7 +10743,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>34</v>
@@ -10778,7 +10784,7 @@
         <v>462</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>463</v>
@@ -10813,7 +10819,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>465</v>
@@ -10858,13 +10864,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c t="s" r="I275" s="7">
         <v>66</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -10890,13 +10896,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>31</v>
@@ -10939,7 +10945,7 @@
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -10966,15 +10972,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -11001,10 +11007,10 @@
         <v>65</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="K279" s="7">
         <v>91</v>
@@ -11056,7 +11062,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -11096,7 +11102,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -11123,10 +11129,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -11161,7 +11167,7 @@
         <v>472</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -11190,7 +11196,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="I285" s="7">
         <v>149</v>
@@ -11222,7 +11228,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>34</v>
@@ -11271,7 +11277,7 @@
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -11354,7 +11360,7 @@
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11384,7 +11390,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -11419,7 +11425,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -11463,7 +11469,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>480</v>
@@ -11495,13 +11501,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>86</v>
@@ -11533,7 +11539,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="I296" s="7">
         <v>136</v>
@@ -11565,16 +11571,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -11614,7 +11620,7 @@
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>356</v>
+        <v>81</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11641,7 +11647,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>175</v>
@@ -11689,7 +11695,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>181</v>
@@ -11815,7 +11821,7 @@
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11839,16 +11845,16 @@
         <v>16</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c t="s" r="K306" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
@@ -11873,7 +11879,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>16</v>
@@ -11882,7 +11888,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="K307" s="7">
         <v>489</v>
@@ -11919,12 +11925,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11951,7 +11957,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>96</v>
@@ -11998,10 +12004,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>116</v>
@@ -12030,7 +12036,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>34</v>
@@ -12109,7 +12115,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -12141,15 +12147,15 @@
         <v>177</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12176,10 +12182,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -12211,10 +12217,10 @@
         <v>497</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -12326,7 +12332,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>143</v>
@@ -12360,7 +12366,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>34</v>
@@ -12400,7 +12406,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c t="s" r="I323" s="7">
         <v>76</v>
@@ -12411,7 +12417,7 @@
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12432,13 +12438,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>504</v>
@@ -12470,7 +12476,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>21</v>
@@ -12480,7 +12486,9 @@
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
-      <c r="M325" s="7"/>
+      <c t="s" r="M325" s="7">
+        <v>507</v>
+      </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
       <c t="s" r="A326" s="6">
@@ -12500,16 +12508,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -12542,7 +12550,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -12554,15 +12562,15 @@
         <v>68</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12577,7 +12585,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12592,12 +12600,12 @@
         <v>141</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12612,7 +12620,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12627,12 +12635,12 @@
         <v>86</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12647,7 +12655,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12667,7 +12675,7 @@
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12682,7 +12690,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12694,7 +12702,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>20</v>
@@ -12702,7 +12710,7 @@
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12717,7 +12725,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12729,7 +12737,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>262</v>
@@ -12737,7 +12745,7 @@
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12763,11 +12771,11 @@
         <v>9854</v>
       </c>
       <c t="s" r="C335" s="7">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12789,7 +12797,7 @@
       </c>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12819,7 +12827,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12834,12 +12842,12 @@
         <v>126</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12854,7 +12862,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12869,12 +12877,12 @@
         <v>161</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12889,7 +12897,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12911,7 +12919,7 @@
       </c>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12926,7 +12934,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12938,17 +12946,17 @@
         <v>34</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>76</v>
       </c>
       <c t="s" r="K340" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12963,7 +12971,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12978,14 +12986,14 @@
         <v>93</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="K341" s="7">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -13000,7 +13008,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -13015,14 +13023,14 @@
         <v>36</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="K342" s="7">
         <v>122</v>
       </c>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -13052,7 +13060,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -13072,7 +13080,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -13087,7 +13095,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -13096,18 +13104,18 @@
         <v>110</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c t="s" r="I345" s="7">
         <v>146</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -13122,19 +13130,19 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>93</v>
@@ -13142,7 +13150,7 @@
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -13157,7 +13165,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -13166,10 +13174,10 @@
         <v>110</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>96</v>
@@ -13192,27 +13200,27 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>263</v>
+        <v>246</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -13242,7 +13250,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -13254,15 +13262,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13277,7 +13285,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -13286,7 +13294,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="I351" s="7">
         <v>86</v>
@@ -13297,7 +13305,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13312,22 +13320,22 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -13347,7 +13355,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -13359,17 +13367,17 @@
         <v>84</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="K353" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13384,7 +13392,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -13399,14 +13407,14 @@
         <v>59</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="K354" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13436,7 +13444,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -13471,7 +13479,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13480,13 +13488,13 @@
         <v>68</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I357" s="7">
         <v>153</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -13506,13 +13514,13 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>68</v>
@@ -13521,12 +13529,12 @@
         <v>36</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -13556,7 +13564,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13591,7 +13599,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13603,7 +13611,7 @@
         <v>177</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>146</v>
@@ -13611,7 +13619,7 @@
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13626,7 +13634,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13646,7 +13654,7 @@
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13661,7 +13669,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13670,18 +13678,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I363" s="7">
         <v>151</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13696,27 +13704,27 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13731,7 +13739,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13746,7 +13754,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -13779,7 +13787,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13799,7 +13807,7 @@
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13814,7 +13822,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13829,7 +13837,7 @@
         <v>137</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -13849,7 +13857,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13864,14 +13872,14 @@
         <v>152</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="K369" s="7">
         <v>36</v>
       </c>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13886,7 +13894,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13934,7 +13942,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13943,7 +13951,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>243</v>
@@ -13954,7 +13962,7 @@
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13969,13 +13977,13 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>16</v>
@@ -13989,7 +13997,7 @@
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -14004,7 +14012,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -14024,7 +14032,7 @@
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -14039,7 +14047,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -14051,15 +14059,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -14074,7 +14082,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -14086,7 +14094,7 @@
         <v>177</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>504</v>
@@ -14096,7 +14104,7 @@
       </c>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -14111,7 +14119,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -14126,14 +14134,14 @@
         <v>19</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c t="s" r="K377" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -14163,7 +14171,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -14183,7 +14191,7 @@
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14198,7 +14206,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -14218,7 +14226,7 @@
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -14233,7 +14241,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -14245,15 +14253,15 @@
         <v>84</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14268,7 +14276,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -14283,10 +14291,10 @@
         <v>108</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="K382" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
@@ -14320,7 +14328,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14332,7 +14340,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>148</v>
@@ -14340,7 +14348,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14355,7 +14363,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14367,15 +14375,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -14390,7 +14398,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -14399,18 +14407,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c t="s" r="I386" s="7">
         <v>155</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14425,22 +14433,22 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -14473,7 +14481,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -14482,7 +14490,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c t="s" r="I389" s="7">
         <v>85</v>
@@ -14508,13 +14516,13 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>16</v>
@@ -14528,7 +14536,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14543,7 +14551,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -14552,16 +14560,16 @@
         <v>16</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c t="s" r="K391" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
@@ -14580,13 +14588,13 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>16</v>
@@ -14595,14 +14603,14 @@
         <v>117</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="K392" s="7">
         <v>137</v>
       </c>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14617,7 +14625,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14626,7 +14634,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>91</v>
@@ -14635,11 +14643,11 @@
         <v>152</v>
       </c>
       <c t="s" r="K393" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14654,29 +14662,29 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>20</v>
       </c>
       <c t="s" r="K394" s="7">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14706,7 +14714,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
@@ -14724,11 +14732,11 @@
         <v>161</v>
       </c>
       <c t="s" r="K396" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14743,7 +14751,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F397" s="7">
         <v>330</v>
@@ -14755,17 +14763,17 @@
         <v>34</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c t="s" r="K397" s="7">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14795,22 +14803,22 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -14841,11 +14849,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C401" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
@@ -14854,10 +14862,10 @@
         <v>65</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>55</v>
@@ -14865,7 +14873,7 @@
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14876,17 +14884,17 @@
         <v>5806</v>
       </c>
       <c t="s" r="C402" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>65</v>
@@ -14895,7 +14903,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -14928,7 +14936,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -14940,7 +14948,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>67</v>
@@ -14963,7 +14971,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -14978,12 +14986,12 @@
         <v>181</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14998,7 +15006,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -15013,12 +15021,12 @@
         <v>167</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -15033,7 +15041,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -15042,18 +15050,18 @@
         <v>65</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c t="s" r="I407" s="7">
         <v>122</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>48</v>
+        <v>411</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -15083,7 +15091,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
@@ -15092,18 +15100,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c t="s" r="I409" s="7">
         <v>439</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -15118,26 +15126,28 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>175</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
-      <c r="M410" s="7"/>
+      <c t="s" r="M410" s="7">
+        <v>582</v>
+      </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
       <c r="A411" s="6"/>
@@ -15166,7 +15176,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -15178,7 +15188,7 @@
         <v>65</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>126</v>
@@ -15186,7 +15196,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15201,7 +15211,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -15210,7 +15220,7 @@
         <v>65</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>141</v>
@@ -15236,27 +15246,27 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>65</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -15286,7 +15296,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -15295,7 +15305,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c t="s" r="I416" s="7">
         <v>86</v>
@@ -15321,13 +15331,13 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>16</v>
@@ -15336,7 +15346,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -15344,7 +15354,7 @@
     </row>
     <row r="418" ht="15.75" customHeight="1">
       <c t="s" r="A418" s="9">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B418" s="9"/>
       <c r="C418" s="9"/>
@@ -15364,7 +15374,7 @@
     <row r="419" ht="65.25" customHeight="1"/>
     <row r="420" ht="17.25" customHeight="1">
       <c t="s" r="A420" s="10">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B420" s="10"/>
       <c r="C420" s="10"/>
@@ -15377,7 +15387,7 @@
       <c r="J420" s="10"/>
       <c r="K420" s="10"/>
       <c t="s" r="L420" s="11">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="M420" s="11"/>
       <c r="N420" s="11"/>

--- a/Data/FlightPlan/FPL_12OCT26.xlsx
+++ b/Data/FlightPlan/FPL_12OCT26.xlsx
@@ -353,6 +353,9 @@
     <t>22:30</t>
   </si>
   <si>
+    <t>23:07</t>
+  </si>
+  <si>
     <t>VN-A526</t>
   </si>
   <si>
@@ -488,6 +491,9 @@
     <t>22:05</t>
   </si>
   <si>
+    <t>23:18</t>
+  </si>
+  <si>
     <t>VN-A532</t>
   </si>
   <si>
@@ -533,6 +539,9 @@
     <t>06:55</t>
   </si>
   <si>
+    <t>01:05</t>
+  </si>
+  <si>
     <t>VN-A534</t>
   </si>
   <si>
@@ -836,309 +845,312 @@
     <t>22:15</t>
   </si>
   <si>
+    <t>05:44</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>15:03</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>15:02</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>12:54</t>
+  </si>
+  <si>
+    <t>16:54</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>19:16</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>21:39</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:18</t>
+  </si>
+  <si>
+    <t>13:54</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>06:56</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>13:08</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>19:19</t>
+  </si>
+  <si>
+    <t>20:54</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>18:39</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>08:53</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>11:19</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>13:36</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>15:29</t>
+  </si>
+  <si>
+    <t>17:23</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>21:57</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>00:35</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>13:38</t>
+  </si>
+  <si>
+    <t>15:34</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>18:29</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>20:01</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>621A *</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>14:03</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>16:34</t>
+  </si>
+  <si>
+    <t>19:22</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>22:27</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>15:41</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>18:01</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>20:03</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
     <t>05:40</t>
   </si>
   <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>15:03</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>15:02</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>12:54</t>
-  </si>
-  <si>
-    <t>16:54</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>19:16</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>21:39</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:18</t>
-  </si>
-  <si>
-    <t>13:54</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>06:56</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>13:08</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>19:19</t>
-  </si>
-  <si>
-    <t>20:54</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>18:39</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>08:53</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>11:19</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>13:36</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>15:29</t>
-  </si>
-  <si>
-    <t>17:23</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>21:57</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>00:35</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>08:59</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>13:38</t>
-  </si>
-  <si>
-    <t>15:34</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>18:29</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>20:01</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>621A *</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>14:03</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>16:34</t>
-  </si>
-  <si>
-    <t>19:22</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>22:27</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>12:53</t>
-  </si>
-  <si>
-    <t>15:41</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>18:01</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>20:03</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
     <t>07:21</t>
   </si>
   <si>
@@ -1277,9 +1289,6 @@
     <t>20:53</t>
   </si>
   <si>
-    <t>01:05</t>
-  </si>
-  <si>
     <t>VN-A646</t>
   </si>
   <si>
@@ -1439,6 +1448,9 @@
     <t>18:41</t>
   </si>
   <si>
+    <t>23:27</t>
+  </si>
+  <si>
     <t>VN-A661</t>
   </si>
   <si>
@@ -1532,7 +1544,7 @@
     <t>01:15</t>
   </si>
   <si>
-    <t>01:14</t>
+    <t>01:24</t>
   </si>
   <si>
     <t>02:20</t>
@@ -1640,12 +1652,18 @@
     <t>17:38</t>
   </si>
   <si>
+    <t>23:42</t>
+  </si>
+  <si>
     <t>VN-A687</t>
   </si>
   <si>
     <t>20:23</t>
   </si>
   <si>
+    <t>22:33</t>
+  </si>
+  <si>
     <t>VN-A689</t>
   </si>
   <si>
@@ -1757,7 +1775,7 @@
     <t>BNE</t>
   </si>
   <si>
-    <t>06:01</t>
+    <t>05:58</t>
   </si>
   <si>
     <t>VN-A817</t>
@@ -1781,10 +1799,13 @@
     <t>06:05</t>
   </si>
   <si>
+    <t>06:38</t>
+  </si>
+  <si>
     <t>Total Record(s): 340</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 12, 2026 21:35</t>
+    <t xml:space="preserve">Generated on  Oct 12, 2026 22:11</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3357,7 +3378,9 @@
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
+      <c t="s" r="M38" s="7">
+        <v>114</v>
+      </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="6"/>
@@ -3386,7 +3409,7 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
@@ -3395,18 +3418,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
       <c t="s" r="M40" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
@@ -3421,13 +3444,13 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G41" s="8">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="H41" s="8">
         <v>16</v>
@@ -3436,12 +3459,12 @@
         <v>88</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c t="s" r="M41" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
@@ -3456,7 +3479,7 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -3465,18 +3488,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H42" s="8">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
       <c t="s" r="M42" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
@@ -3491,22 +3514,22 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="H43" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -3539,7 +3562,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -3551,15 +3574,15 @@
         <v>84</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c t="s" r="M45" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -3574,7 +3597,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -3594,7 +3617,7 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c t="s" r="M46" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -3609,7 +3632,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -3618,18 +3641,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c t="s" r="M47" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -3644,27 +3667,27 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G48" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="H48" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c t="s" r="M48" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
@@ -3679,7 +3702,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3714,7 +3737,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3723,13 +3746,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3762,7 +3785,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3777,12 +3800,12 @@
         <v>29</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c t="s" r="M52" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
@@ -3797,7 +3820,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3809,15 +3832,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c t="s" r="M53" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -3832,7 +3855,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3844,15 +3867,15 @@
         <v>84</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c t="s" r="M54" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
@@ -3867,7 +3890,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3879,13 +3902,13 @@
         <v>34</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="K55" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L55" s="7"/>
       <c t="s" r="M55" s="7">
@@ -3904,7 +3927,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3916,15 +3939,15 @@
         <v>110</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c t="s" r="M56" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -3939,7 +3962,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3951,14 +3974,16 @@
         <v>34</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
-      <c r="M57" s="7"/>
+      <c t="s" r="M57" s="7">
+        <v>160</v>
+      </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="6"/>
@@ -3987,7 +4012,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3999,15 +4024,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
       <c t="s" r="M59" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
@@ -4022,7 +4047,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -4037,12 +4062,12 @@
         <v>67</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c t="s" r="M60" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -4057,7 +4082,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -4069,7 +4094,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J61" s="7">
         <v>56</v>
@@ -4092,7 +4117,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -4104,17 +4129,17 @@
         <v>110</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="K62" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L62" s="7"/>
       <c t="s" r="M62" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
@@ -4129,7 +4154,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -4141,7 +4166,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J63" s="7">
         <v>37</v>
@@ -4151,7 +4176,7 @@
       </c>
       <c r="L63" s="7"/>
       <c t="s" r="M63" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -4166,7 +4191,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -4178,14 +4203,18 @@
         <v>83</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>173</v>
-      </c>
-      <c r="K64" s="7"/>
+        <v>175</v>
+      </c>
+      <c t="s" r="K64" s="7">
+        <v>176</v>
+      </c>
       <c r="L64" s="7"/>
-      <c r="M64" s="7"/>
+      <c t="s" r="M64" s="7">
+        <v>100</v>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="6"/>
@@ -4214,7 +4243,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -4226,15 +4255,15 @@
         <v>99</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c t="s" r="M66" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -4249,7 +4278,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -4258,18 +4287,18 @@
         <v>99</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c t="s" r="M67" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -4284,27 +4313,27 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>99</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c t="s" r="M68" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -4319,7 +4348,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -4334,7 +4363,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -4354,7 +4383,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -4363,18 +4392,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c t="s" r="M70" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -4389,27 +4418,27 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="H71" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -4424,7 +4453,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -4436,15 +4465,15 @@
         <v>99</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c t="s" r="M72" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -4459,7 +4488,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -4471,15 +4500,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c t="s" r="M73" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -4509,27 +4538,27 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4544,7 +4573,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4556,15 +4585,15 @@
         <v>110</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4579,7 +4608,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4591,15 +4620,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4614,7 +4643,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4636,7 +4665,7 @@
       </c>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4651,7 +4680,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4663,13 +4692,13 @@
         <v>34</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J79" s="7">
         <v>21</v>
       </c>
       <c t="s" r="K79" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
@@ -4688,7 +4717,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4697,10 +4726,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J80" s="7">
         <v>100</v>
@@ -4736,7 +4765,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4748,15 +4777,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c t="s" r="M82" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -4771,7 +4800,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4783,7 +4812,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c t="s" r="J83" s="7">
         <v>95</v>
@@ -4791,7 +4820,7 @@
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4821,7 +4850,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4830,18 +4859,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4856,27 +4885,27 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="H86" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4891,7 +4920,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4903,7 +4932,7 @@
         <v>99</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="J87" s="7">
         <v>35</v>
@@ -4928,7 +4957,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4940,15 +4969,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4963,7 +4992,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4975,15 +5004,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4998,7 +5027,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -5010,7 +5039,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>28</v>
@@ -5046,7 +5075,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -5055,18 +5084,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -5081,27 +5110,27 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="H93" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -5116,7 +5145,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -5128,7 +5157,7 @@
         <v>99</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J94" s="7">
         <v>91</v>
@@ -5136,7 +5165,7 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -5151,7 +5180,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -5163,15 +5192,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -5186,7 +5215,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -5195,10 +5224,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>26</v>
@@ -5206,7 +5235,7 @@
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -5221,22 +5250,22 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c t="s" r="H97" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -5265,31 +5294,31 @@
         <v>7615</v>
       </c>
       <c t="s" r="C99" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -5300,11 +5329,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C100" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5316,7 +5345,7 @@
         <v>65</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c t="s" r="J100" s="7">
         <v>69</v>
@@ -5324,7 +5353,7 @@
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -5339,7 +5368,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -5351,15 +5380,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -5374,7 +5403,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5386,17 +5415,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c t="s" r="K102" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5411,7 +5440,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5423,7 +5452,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>67</v>
@@ -5459,7 +5488,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5471,15 +5500,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c t="s" r="M105" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
@@ -5494,7 +5523,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5506,15 +5535,15 @@
         <v>84</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c t="s" r="M106" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -5529,7 +5558,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5541,15 +5570,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5579,27 +5608,27 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c t="s" r="M109" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -5614,7 +5643,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5634,7 +5663,7 @@
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5649,7 +5678,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5661,15 +5690,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5684,7 +5713,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5696,15 +5725,15 @@
         <v>84</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5719,7 +5748,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5731,10 +5760,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5767,29 +5796,29 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c t="s" r="J115" s="7">
         <v>70</v>
       </c>
       <c t="s" r="K115" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5804,7 +5833,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5822,11 +5851,11 @@
         <v>32</v>
       </c>
       <c t="s" r="K116" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5841,7 +5870,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5853,15 +5882,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5876,7 +5905,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5888,17 +5917,17 @@
         <v>84</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="K118" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5913,7 +5942,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5925,17 +5954,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c t="s" r="K119" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5965,7 +5994,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5974,18 +6003,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c t="s" r="I121" s="7">
         <v>100</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -6000,27 +6029,27 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -6035,7 +6064,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -6044,13 +6073,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c t="s" r="I123" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -6083,7 +6112,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -6092,10 +6121,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>108</v>
@@ -6118,19 +6147,19 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>79</v>
@@ -6138,7 +6167,7 @@
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -6153,7 +6182,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -6165,10 +6194,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -6201,7 +6230,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6213,7 +6242,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>103</v>
@@ -6221,7 +6250,7 @@
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -6236,7 +6265,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6248,15 +6277,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6271,7 +6300,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6283,17 +6312,17 @@
         <v>110</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="K131" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6308,7 +6337,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6320,17 +6349,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="K132" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -6345,7 +6374,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6354,16 +6383,16 @@
         <v>16</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="K133" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
@@ -6382,13 +6411,13 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>16</v>
@@ -6397,10 +6426,10 @@
         <v>36</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="K134" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
@@ -6434,7 +6463,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6443,7 +6472,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="I136" s="7">
         <v>100</v>
@@ -6454,7 +6483,7 @@
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -6469,27 +6498,27 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6504,7 +6533,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6513,18 +6542,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c t="s" r="I138" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6539,22 +6568,22 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6587,13 +6616,13 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>16</v>
@@ -6602,12 +6631,12 @@
         <v>69</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6622,7 +6651,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6631,18 +6660,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6657,27 +6686,27 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6707,7 +6736,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6719,15 +6748,15 @@
         <v>68</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6742,7 +6771,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6754,7 +6783,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>55</v>
@@ -6762,7 +6791,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6777,7 +6806,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6789,7 +6818,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>91</v>
@@ -6827,7 +6856,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6836,13 +6865,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6862,27 +6891,27 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6912,7 +6941,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6924,15 +6953,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6947,7 +6976,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6959,7 +6988,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>103</v>
@@ -6967,7 +6996,7 @@
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6982,7 +7011,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6991,18 +7020,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -7017,27 +7046,27 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -7052,7 +7081,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -7061,7 +7090,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="I156" s="7">
         <v>108</v>
@@ -7072,7 +7101,7 @@
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -7087,19 +7116,19 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>39</v>
@@ -7107,7 +7136,7 @@
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -7137,7 +7166,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -7149,7 +7178,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>18</v>
@@ -7157,7 +7186,7 @@
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -7172,7 +7201,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7181,18 +7210,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7207,13 +7236,13 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>34</v>
@@ -7222,12 +7251,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -7242,7 +7271,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7254,10 +7283,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -7290,7 +7319,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7299,18 +7328,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7325,27 +7354,27 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7360,7 +7389,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7372,17 +7401,17 @@
         <v>110</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c t="s" r="K166" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7397,7 +7426,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7406,18 +7435,18 @@
         <v>110</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -7432,27 +7461,27 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7467,7 +7496,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7479,15 +7508,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7502,7 +7531,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7517,14 +7546,14 @@
         <v>37</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c t="s" r="K170" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7539,7 +7568,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7551,17 +7580,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c t="s" r="K171" s="7">
         <v>60</v>
       </c>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7576,7 +7605,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7591,10 +7620,10 @@
         <v>44</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c t="s" r="K172" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
@@ -7628,7 +7657,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7637,18 +7666,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7663,27 +7692,27 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7698,7 +7727,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7707,10 +7736,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>55</v>
@@ -7718,7 +7747,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7733,27 +7762,27 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7768,7 +7797,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7777,18 +7806,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="I178" s="7">
         <v>93</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7803,19 +7832,19 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>59</v>
@@ -7823,7 +7852,7 @@
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7838,7 +7867,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7850,17 +7879,17 @@
         <v>34</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>81</v>
       </c>
       <c t="s" r="K180" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7890,7 +7919,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7902,15 +7931,15 @@
         <v>110</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7918,14 +7947,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B183" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7937,17 +7966,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c t="s" r="K183" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7962,7 +7991,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7974,17 +8003,17 @@
         <v>68</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c t="s" r="K184" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -7999,7 +8028,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -8011,17 +8040,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>88</v>
       </c>
       <c t="s" r="K185" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -8036,7 +8065,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -8048,7 +8077,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>19</v>
@@ -8056,7 +8085,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -8071,7 +8100,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -8083,15 +8112,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -8121,7 +8150,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8130,7 +8159,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>103</v>
@@ -8141,7 +8170,7 @@
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -8156,29 +8185,29 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="K190" s="7">
         <v>55</v>
       </c>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -8193,7 +8222,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8202,20 +8231,20 @@
         <v>34</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c t="s" r="K191" s="7">
         <v>35</v>
       </c>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8230,29 +8259,29 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c t="s" r="K192" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8282,7 +8311,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8294,15 +8323,15 @@
         <v>110</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>275</v>
+        <v>379</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -8317,7 +8346,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8329,15 +8358,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8352,7 +8381,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8361,20 +8390,20 @@
         <v>34</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="K196" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8389,13 +8418,13 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>34</v>
@@ -8407,11 +8436,11 @@
         <v>70</v>
       </c>
       <c t="s" r="K197" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8426,7 +8455,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8438,7 +8467,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>35</v>
@@ -8446,7 +8475,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8461,7 +8490,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8473,7 +8502,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>38</v>
@@ -8481,7 +8510,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8496,7 +8525,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8511,7 +8540,7 @@
         <v>113</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -8529,7 +8558,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8541,10 +8570,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -8577,7 +8606,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8589,15 +8618,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8612,7 +8641,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8624,15 +8653,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8647,7 +8676,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8659,15 +8688,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8682,7 +8711,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8691,18 +8720,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="I206" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8717,27 +8746,27 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="H207" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8752,7 +8781,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8761,18 +8790,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8787,27 +8816,27 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8837,7 +8866,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8849,15 +8878,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8872,7 +8901,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8884,10 +8913,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8907,7 +8936,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8919,15 +8948,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8942,7 +8971,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8954,7 +8983,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>38</v>
@@ -8962,7 +8991,7 @@
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8992,7 +9021,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -9001,18 +9030,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -9027,27 +9056,27 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -9062,7 +9091,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -9071,18 +9100,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -9097,27 +9126,27 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -9132,7 +9161,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9141,20 +9170,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c t="s" r="K220" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9169,29 +9198,29 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c t="s" r="K221" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9221,7 +9250,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9230,18 +9259,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -9256,13 +9285,13 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>34</v>
@@ -9271,12 +9300,12 @@
         <v>53</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -9291,7 +9320,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9300,18 +9329,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9326,27 +9355,27 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9361,7 +9390,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9373,10 +9402,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>422</v>
+        <v>176</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -9409,19 +9438,19 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>72</v>
@@ -9429,7 +9458,7 @@
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9444,7 +9473,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9453,10 +9482,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>26</v>
@@ -9464,7 +9493,7 @@
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9479,22 +9508,22 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -9527,7 +9556,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9539,15 +9568,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9562,7 +9591,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9571,18 +9600,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c t="s" r="I234" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9597,27 +9626,27 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9632,7 +9661,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9644,7 +9673,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>100</v>
@@ -9680,7 +9709,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9692,7 +9721,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>88</v>
@@ -9700,7 +9729,7 @@
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9715,7 +9744,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9727,17 +9756,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c t="s" r="K239" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9752,7 +9781,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9764,13 +9793,13 @@
         <v>34</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="K240" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
@@ -9804,7 +9833,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9813,18 +9842,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9839,27 +9868,27 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9874,7 +9903,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9886,7 +9915,7 @@
         <v>84</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>76</v>
@@ -9909,7 +9938,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9921,15 +9950,15 @@
         <v>110</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9959,7 +9988,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F247" s="7">
         <v>320</v>
@@ -9968,13 +9997,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9994,19 +10023,19 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F248" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>27</v>
@@ -10014,7 +10043,7 @@
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -10029,7 +10058,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F249" s="7">
         <v>320</v>
@@ -10041,15 +10070,15 @@
         <v>84</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -10064,7 +10093,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F250" s="7">
         <v>320</v>
@@ -10076,15 +10105,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -10099,7 +10128,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F251" s="7">
         <v>320</v>
@@ -10108,18 +10137,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c t="s" r="I251" s="7">
         <v>72</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -10134,13 +10163,13 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F252" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>16</v>
@@ -10149,12 +10178,12 @@
         <v>73</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -10169,7 +10198,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -10178,18 +10207,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c t="s" r="I253" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10204,19 +10233,19 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>79</v>
@@ -10224,7 +10253,7 @@
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10254,7 +10283,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -10266,15 +10295,15 @@
         <v>110</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10289,7 +10318,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -10301,15 +10330,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10324,7 +10353,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10344,7 +10373,7 @@
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10359,7 +10388,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -10368,18 +10397,18 @@
         <v>110</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10394,27 +10423,27 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10444,7 +10473,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10456,15 +10485,15 @@
         <v>84</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10479,7 +10508,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10494,12 +10523,12 @@
         <v>52</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10514,7 +10543,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10523,18 +10552,18 @@
         <v>110</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10549,19 +10578,19 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>38</v>
@@ -10569,7 +10598,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10584,7 +10613,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10593,7 +10622,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c t="s" r="I266" s="7">
         <v>62</v>
@@ -10632,7 +10661,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -10644,15 +10673,15 @@
         <v>84</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10667,7 +10696,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -10679,7 +10708,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>55</v>
@@ -10687,7 +10716,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10702,7 +10731,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -10711,18 +10740,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10737,13 +10766,13 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>34</v>
@@ -10752,12 +10781,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10772,7 +10801,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -10781,18 +10810,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10807,22 +10836,22 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -10855,7 +10884,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10864,18 +10893,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="I275" s="7">
         <v>66</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10890,19 +10919,19 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>31</v>
@@ -10910,7 +10939,7 @@
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10925,7 +10954,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10937,15 +10966,15 @@
         <v>110</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -10960,7 +10989,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10972,15 +11001,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10995,7 +11024,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -11007,17 +11036,17 @@
         <v>65</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="K279" s="7">
         <v>91</v>
       </c>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -11047,7 +11076,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -11062,12 +11091,12 @@
         <v>63</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -11082,7 +11111,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -11094,15 +11123,15 @@
         <v>84</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -11117,7 +11146,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -11129,10 +11158,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -11152,7 +11181,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -11164,15 +11193,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -11187,7 +11216,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -11196,10 +11225,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>56</v>
@@ -11207,7 +11236,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -11222,27 +11251,27 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11257,7 +11286,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -11272,12 +11301,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -11292,7 +11321,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -11311,7 +11340,9 @@
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
-      <c r="M288" s="7"/>
+      <c t="s" r="M288" s="7">
+        <v>479</v>
+      </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
       <c r="A289" s="6"/>
@@ -11340,7 +11371,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11352,15 +11383,15 @@
         <v>65</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11375,7 +11406,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11387,15 +11418,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11410,7 +11441,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11425,12 +11456,12 @@
         <v>59</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11460,7 +11491,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -11469,10 +11500,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>52</v>
@@ -11480,7 +11511,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11495,19 +11526,19 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>86</v>
@@ -11515,7 +11546,7 @@
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11530,7 +11561,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11539,10 +11570,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>73</v>
@@ -11550,7 +11581,7 @@
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11565,27 +11596,27 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11600,7 +11631,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11609,13 +11640,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c t="s" r="I298" s="7">
         <v>92</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -11635,22 +11666,22 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>422</v>
+        <v>176</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -11683,7 +11714,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11695,15 +11726,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11718,7 +11749,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11730,7 +11761,7 @@
         <v>65</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>32</v>
@@ -11753,7 +11784,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11765,10 +11796,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -11801,7 +11832,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -11813,15 +11844,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11836,7 +11867,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11845,20 +11876,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c t="s" r="K306" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11873,13 +11904,13 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>16</v>
@@ -11888,14 +11919,14 @@
         <v>70</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c t="s" r="K307" s="7">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11910,7 +11941,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11919,18 +11950,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="I308" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11945,19 +11976,19 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>96</v>
@@ -11995,7 +12026,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -12004,18 +12035,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -12030,27 +12061,27 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -12065,7 +12096,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -12077,7 +12108,7 @@
         <v>84</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>106</v>
@@ -12085,7 +12116,7 @@
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -12100,7 +12131,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -12115,12 +12146,12 @@
         <v>88</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -12135,7 +12166,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -12144,18 +12175,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12170,27 +12201,27 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12205,7 +12236,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -12214,13 +12245,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -12253,7 +12284,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -12265,15 +12296,15 @@
         <v>65</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12288,7 +12319,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -12300,15 +12331,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12323,7 +12354,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -12332,20 +12363,20 @@
         <v>34</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="K321" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -12360,29 +12391,29 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>88</v>
       </c>
       <c t="s" r="K322" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12397,7 +12428,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12406,18 +12437,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="I323" s="7">
         <v>76</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12432,27 +12463,27 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12467,7 +12498,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12476,18 +12507,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12502,22 +12533,22 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -12550,7 +12581,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -12562,15 +12593,15 @@
         <v>68</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12585,7 +12616,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12597,15 +12628,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12620,7 +12651,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12629,18 +12660,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c t="s" r="I330" s="7">
         <v>86</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12655,27 +12686,27 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12690,7 +12721,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12702,7 +12733,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>20</v>
@@ -12710,7 +12741,7 @@
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12725,7 +12756,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12737,15 +12768,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12771,11 +12802,11 @@
         <v>9854</v>
       </c>
       <c t="s" r="C335" s="7">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12787,17 +12818,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="K335" s="7">
         <v>33</v>
       </c>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12827,7 +12858,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12839,15 +12870,15 @@
         <v>84</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12862,7 +12893,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12874,15 +12905,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12897,7 +12928,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12909,17 +12940,17 @@
         <v>65</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="K339" s="7">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12934,7 +12965,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12946,17 +12977,17 @@
         <v>34</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>76</v>
       </c>
       <c t="s" r="K340" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12971,7 +13002,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12986,14 +13017,14 @@
         <v>93</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="K341" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -13008,7 +13039,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -13023,14 +13054,14 @@
         <v>36</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c t="s" r="K342" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -13060,7 +13091,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -13072,7 +13103,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>67</v>
@@ -13080,7 +13111,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -13095,7 +13126,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -13104,18 +13135,18 @@
         <v>110</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -13130,19 +13161,19 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>93</v>
@@ -13150,7 +13181,7 @@
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -13165,7 +13196,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -13174,10 +13205,10 @@
         <v>110</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>96</v>
@@ -13200,27 +13231,27 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -13250,7 +13281,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -13262,15 +13293,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13285,7 +13316,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -13294,18 +13325,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="I351" s="7">
         <v>86</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13320,22 +13351,22 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -13355,7 +13386,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -13367,17 +13398,17 @@
         <v>84</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="K353" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13392,7 +13423,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -13407,14 +13438,14 @@
         <v>59</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="K354" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13444,7 +13475,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -13456,15 +13487,15 @@
         <v>68</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -13479,7 +13510,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13488,18 +13519,18 @@
         <v>68</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13514,13 +13545,13 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>68</v>
@@ -13529,12 +13560,12 @@
         <v>36</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -13564,7 +13595,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13576,7 +13607,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>29</v>
@@ -13584,7 +13615,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13599,7 +13630,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13608,18 +13639,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13634,27 +13665,27 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13669,7 +13700,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13678,18 +13709,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13704,27 +13735,27 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13739,7 +13770,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13754,11 +13785,13 @@
         <v>39</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
-      <c r="M365" s="7"/>
+      <c t="s" r="M365" s="7">
+        <v>547</v>
+      </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
       <c r="A366" s="6"/>
@@ -13787,7 +13820,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13802,12 +13835,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13822,7 +13855,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13834,15 +13867,15 @@
         <v>68</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13857,7 +13890,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13869,17 +13902,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c t="s" r="K369" s="7">
         <v>36</v>
       </c>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13894,7 +13927,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13913,7 +13946,9 @@
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
-      <c r="M370" s="7"/>
+      <c t="s" r="M370" s="7">
+        <v>550</v>
+      </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
       <c r="A371" s="6"/>
@@ -13942,7 +13977,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13951,18 +13986,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>546</v>
+        <v>552</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13977,19 +14012,19 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>104</v>
@@ -13997,7 +14032,7 @@
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -14012,7 +14047,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -14024,15 +14059,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -14047,7 +14082,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -14059,15 +14094,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>548</v>
+        <v>554</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -14082,7 +14117,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -14091,20 +14126,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c t="s" r="K376" s="7">
         <v>37</v>
       </c>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -14119,13 +14154,13 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>16</v>
@@ -14134,14 +14169,14 @@
         <v>19</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c t="s" r="K377" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>550</v>
+        <v>556</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -14171,7 +14206,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -14183,15 +14218,15 @@
         <v>84</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>552</v>
+        <v>558</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14206,7 +14241,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -14221,12 +14256,12 @@
         <v>101</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -14241,7 +14276,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -14253,15 +14288,15 @@
         <v>84</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>553</v>
+        <v>559</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14276,7 +14311,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -14291,10 +14326,10 @@
         <v>108</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="K382" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
@@ -14328,7 +14363,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14340,15 +14375,15 @@
         <v>51</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14363,7 +14398,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14375,15 +14410,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -14398,7 +14433,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -14407,18 +14442,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>558</v>
+        <v>564</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14433,22 +14468,22 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -14481,7 +14516,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -14490,18 +14525,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="I389" s="7">
         <v>85</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14516,27 +14551,27 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14551,7 +14586,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -14560,16 +14595,16 @@
         <v>16</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c t="s" r="K391" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
@@ -14588,29 +14623,29 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="K392" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14625,7 +14660,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14634,20 +14669,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="K393" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>562</v>
+        <v>568</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14662,29 +14697,29 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>20</v>
       </c>
       <c t="s" r="K394" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>563</v>
+        <v>569</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14714,7 +14749,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
@@ -14726,17 +14761,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="K396" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14751,7 +14786,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="F397" s="7">
         <v>330</v>
@@ -14763,17 +14798,17 @@
         <v>34</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c t="s" r="K397" s="7">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>567</v>
+        <v>573</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14803,27 +14838,27 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14849,11 +14884,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C401" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
@@ -14862,10 +14897,10 @@
         <v>65</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>55</v>
@@ -14873,7 +14908,7 @@
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14884,17 +14919,17 @@
         <v>5806</v>
       </c>
       <c t="s" r="C402" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>65</v>
@@ -14903,11 +14938,13 @@
         <v>33</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
-      <c r="M402" s="7"/>
+      <c t="s" r="M402" s="7">
+        <v>214</v>
+      </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
       <c r="A403" s="6"/>
@@ -14936,7 +14973,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -14948,7 +14985,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>67</v>
@@ -14956,7 +14993,7 @@
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -14971,7 +15008,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -14983,15 +15020,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -15006,7 +15043,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -15018,15 +15055,15 @@
         <v>65</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -15041,7 +15078,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -15050,18 +15087,18 @@
         <v>65</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -15091,7 +15128,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
@@ -15100,18 +15137,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -15126,27 +15163,27 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>582</v>
+        <v>588</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -15176,7 +15213,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -15188,15 +15225,15 @@
         <v>65</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15211,7 +15248,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -15220,10 +15257,10 @@
         <v>65</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>76</v>
@@ -15231,7 +15268,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15246,27 +15283,27 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>65</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -15296,7 +15333,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -15305,7 +15342,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c t="s" r="I416" s="7">
         <v>86</v>
@@ -15316,7 +15353,7 @@
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15331,13 +15368,13 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>16</v>
@@ -15346,15 +15383,17 @@
         <v>43</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
-      <c r="M417" s="7"/>
+      <c t="s" r="M417" s="7">
+        <v>596</v>
+      </c>
     </row>
     <row r="418" ht="15.75" customHeight="1">
       <c t="s" r="A418" s="9">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="B418" s="9"/>
       <c r="C418" s="9"/>
@@ -15374,7 +15413,7 @@
     <row r="419" ht="65.25" customHeight="1"/>
     <row r="420" ht="17.25" customHeight="1">
       <c t="s" r="A420" s="10">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="B420" s="10"/>
       <c r="C420" s="10"/>
@@ -15387,7 +15426,7 @@
       <c r="J420" s="10"/>
       <c r="K420" s="10"/>
       <c t="s" r="L420" s="11">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="M420" s="11"/>
       <c r="N420" s="11"/>

--- a/Data/FlightPlan/FPL_12OCT26.xlsx
+++ b/Data/FlightPlan/FPL_12OCT26.xlsx
@@ -146,7 +146,7 @@
     <t>23:00</t>
   </si>
   <si>
-    <t>02:45</t>
+    <t>02:56</t>
   </si>
   <si>
     <t>02:30</t>
@@ -491,7 +491,7 @@
     <t>22:05</t>
   </si>
   <si>
-    <t>23:18</t>
+    <t>23:28</t>
   </si>
   <si>
     <t>VN-A532</t>
@@ -692,6 +692,9 @@
     <t>23:25</t>
   </si>
   <si>
+    <t>01:39</t>
+  </si>
+  <si>
     <t>VN-A544</t>
   </si>
   <si>
@@ -773,6 +776,12 @@
     <t>02:35</t>
   </si>
   <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
     <t>VN-A551</t>
   </si>
   <si>
@@ -815,6 +824,9 @@
     <t>23:10</t>
   </si>
   <si>
+    <t>06:59</t>
+  </si>
+  <si>
     <t>VN-A553</t>
   </si>
   <si>
@@ -845,7 +857,7 @@
     <t>22:15</t>
   </si>
   <si>
-    <t>05:44</t>
+    <t>05:47</t>
   </si>
   <si>
     <t>VN-A554</t>
@@ -944,9 +956,6 @@
     <t>RMQ</t>
   </si>
   <si>
-    <t>10:10</t>
-  </si>
-  <si>
     <t>18:20</t>
   </si>
   <si>
@@ -1004,6 +1013,9 @@
     <t>05:30</t>
   </si>
   <si>
+    <t>06:06</t>
+  </si>
+  <si>
     <t>VN-A634</t>
   </si>
   <si>
@@ -1049,10 +1061,10 @@
     <t>22:00</t>
   </si>
   <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>00:35</t>
+    <t>00:57</t>
+  </si>
+  <si>
+    <t>01:50</t>
   </si>
   <si>
     <t>VN-A635</t>
@@ -1088,6 +1100,9 @@
     <t>23:30</t>
   </si>
   <si>
+    <t>01:43</t>
+  </si>
+  <si>
     <t>VN-A636</t>
   </si>
   <si>
@@ -1169,12 +1184,12 @@
     <t>16:09</t>
   </si>
   <si>
+    <t>01:22</t>
+  </si>
+  <si>
     <t>02:10</t>
   </si>
   <si>
-    <t>03:05</t>
-  </si>
-  <si>
     <t>VN-A641</t>
   </si>
   <si>
@@ -1253,270 +1268,276 @@
     <t>22:25</t>
   </si>
   <si>
+    <t>02:51</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>03:40</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>11:37</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>14:41</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>20:53</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>14:24</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>00:43</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>18:06</t>
+  </si>
+  <si>
+    <t>20:38</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>15:21</t>
+  </si>
+  <si>
+    <t>17:54</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>13:12</t>
+  </si>
+  <si>
+    <t>18:17</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>08:29</t>
+  </si>
+  <si>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>19:53</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>10:53</t>
+  </si>
+  <si>
+    <t>12:47</t>
+  </si>
+  <si>
+    <t>15:18</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>09:02</t>
+  </si>
+  <si>
+    <t>11:42</t>
+  </si>
+  <si>
+    <t>17:12</t>
+  </si>
+  <si>
+    <t>19:07</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>16:08</t>
+  </si>
+  <si>
+    <t>18:46</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>00:19</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>09:03</t>
+  </si>
+  <si>
+    <t>11:44</t>
+  </si>
+  <si>
+    <t>18:23</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>14:12</t>
+  </si>
+  <si>
+    <t>16:42</t>
+  </si>
+  <si>
+    <t>18:41</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>18:18</t>
+  </si>
+  <si>
+    <t>22:49</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:41</t>
+  </si>
+  <si>
+    <t>11:08</t>
+  </si>
+  <si>
+    <t>14:53</t>
+  </si>
+  <si>
+    <t>17:19</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>11:09</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>05:57</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>08:56</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>13:48</t>
+  </si>
+  <si>
+    <t>16:32</t>
+  </si>
+  <si>
+    <t>21:37</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
     <t>02:40</t>
   </si>
   <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>03:40</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>11:37</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>14:41</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>20:53</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>14:24</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>00:43</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>18:06</t>
-  </si>
-  <si>
-    <t>20:38</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>15:21</t>
-  </si>
-  <si>
-    <t>17:54</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>13:12</t>
-  </si>
-  <si>
-    <t>18:17</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>08:29</t>
-  </si>
-  <si>
-    <t>12:12</t>
-  </si>
-  <si>
-    <t>19:53</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>10:53</t>
-  </si>
-  <si>
-    <t>12:47</t>
-  </si>
-  <si>
-    <t>15:18</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>09:02</t>
-  </si>
-  <si>
-    <t>11:42</t>
-  </si>
-  <si>
-    <t>17:12</t>
-  </si>
-  <si>
-    <t>19:07</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>16:08</t>
-  </si>
-  <si>
-    <t>18:46</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>00:19</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>09:03</t>
-  </si>
-  <si>
-    <t>11:44</t>
-  </si>
-  <si>
-    <t>18:23</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>14:12</t>
-  </si>
-  <si>
-    <t>16:42</t>
-  </si>
-  <si>
-    <t>18:41</t>
-  </si>
-  <si>
-    <t>23:27</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>18:18</t>
-  </si>
-  <si>
-    <t>22:49</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:41</t>
-  </si>
-  <si>
-    <t>11:08</t>
-  </si>
-  <si>
-    <t>14:53</t>
-  </si>
-  <si>
-    <t>17:19</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>11:09</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>08:56</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>13:48</t>
-  </si>
-  <si>
-    <t>16:32</t>
-  </si>
-  <si>
-    <t>21:37</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
     <t>VN-A672</t>
   </si>
   <si>
@@ -1805,7 +1826,7 @@
     <t>Total Record(s): 340</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 12, 2026 22:11</t>
+    <t xml:space="preserve">Generated on  Oct 13, 2026 00:00</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5046,7 +5067,9 @@
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
-      <c r="M90" s="7"/>
+      <c t="s" r="M90" s="7">
+        <v>227</v>
+      </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="6"/>
@@ -5075,7 +5098,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -5084,18 +5107,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -5110,13 +5133,13 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="H93" s="8">
         <v>16</v>
@@ -5130,7 +5153,7 @@
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -5145,7 +5168,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -5165,7 +5188,7 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -5180,7 +5203,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -5192,10 +5215,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -5215,7 +5238,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -5224,10 +5247,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>26</v>
@@ -5235,7 +5258,7 @@
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -5250,22 +5273,22 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="H97" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -5294,23 +5317,23 @@
         <v>7615</v>
       </c>
       <c t="s" r="C99" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>216</v>
@@ -5318,7 +5341,7 @@
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -5329,11 +5352,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C100" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5345,7 +5368,7 @@
         <v>65</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J100" s="7">
         <v>69</v>
@@ -5353,7 +5376,7 @@
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -5368,7 +5391,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -5380,7 +5403,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J101" s="7">
         <v>223</v>
@@ -5388,7 +5411,7 @@
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -5403,7 +5426,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5415,17 +5438,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="K102" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5440,7 +5463,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5452,14 +5475,18 @@
         <v>17</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>67</v>
       </c>
-      <c r="K103" s="7"/>
+      <c t="s" r="K103" s="7">
+        <v>255</v>
+      </c>
       <c r="L103" s="7"/>
-      <c r="M103" s="7"/>
+      <c t="s" r="M103" s="7">
+        <v>256</v>
+      </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
       <c r="A104" s="6"/>
@@ -5488,7 +5515,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5508,7 +5535,7 @@
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c t="s" r="M105" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
@@ -5523,7 +5550,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5538,7 +5565,7 @@
         <v>219</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -5558,7 +5585,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5573,12 +5600,12 @@
         <v>153</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5608,13 +5635,13 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>34</v>
@@ -5623,7 +5650,7 @@
         <v>217</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5643,7 +5670,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5663,7 +5690,7 @@
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5678,7 +5705,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5693,12 +5720,12 @@
         <v>169</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5713,7 +5740,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5728,12 +5755,12 @@
         <v>156</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5748,7 +5775,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5760,14 +5787,16 @@
         <v>83</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>214</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
-      <c r="M113" s="7"/>
+      <c t="s" r="M113" s="7">
+        <v>271</v>
+      </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c r="A114" s="6"/>
@@ -5796,29 +5825,29 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J115" s="7">
         <v>70</v>
       </c>
       <c t="s" r="K115" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5833,7 +5862,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5855,7 +5884,7 @@
       </c>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5870,7 +5899,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5885,7 +5914,7 @@
         <v>169</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5905,7 +5934,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5920,14 +5949,14 @@
         <v>221</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="K118" s="7">
         <v>223</v>
       </c>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5942,7 +5971,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5957,14 +5986,14 @@
         <v>190</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="K119" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5994,7 +6023,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -6003,7 +6032,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c t="s" r="I121" s="7">
         <v>100</v>
@@ -6014,7 +6043,7 @@
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -6029,13 +6058,13 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>34</v>
@@ -6049,7 +6078,7 @@
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -6064,7 +6093,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -6073,7 +6102,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c t="s" r="I123" s="7">
         <v>22</v>
@@ -6112,7 +6141,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -6147,7 +6176,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -6159,7 +6188,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>79</v>
@@ -6167,7 +6196,7 @@
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -6182,7 +6211,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -6194,7 +6223,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>215</v>
@@ -6230,7 +6259,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6242,7 +6271,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>103</v>
@@ -6265,7 +6294,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6277,7 +6306,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>147</v>
@@ -6300,7 +6329,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6315,14 +6344,14 @@
         <v>149</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c t="s" r="K131" s="7">
         <v>118</v>
       </c>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6337,7 +6366,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6349,7 +6378,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>154</v>
@@ -6374,7 +6403,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6389,7 +6418,7 @@
         <v>220</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="K133" s="7">
         <v>201</v>
@@ -6411,7 +6440,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6426,10 +6455,10 @@
         <v>36</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="K134" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
@@ -6463,7 +6492,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6483,7 +6512,7 @@
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -6498,7 +6527,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6513,12 +6542,12 @@
         <v>209</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6533,7 +6562,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6542,7 +6571,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c t="s" r="I138" s="7">
         <v>19</v>
@@ -6553,7 +6582,7 @@
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6568,13 +6597,13 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>16</v>
@@ -6583,7 +6612,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6616,13 +6645,13 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>16</v>
@@ -6651,7 +6680,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6660,10 +6689,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>155</v>
@@ -6671,7 +6700,7 @@
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6686,13 +6715,13 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>16</v>
@@ -6701,12 +6730,12 @@
         <v>203</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6736,7 +6765,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6748,15 +6777,15 @@
         <v>68</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6771,7 +6800,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6791,7 +6820,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6806,7 +6835,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6818,7 +6847,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>91</v>
@@ -6856,7 +6885,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6865,10 +6894,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>311</v>
+        <v>256</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>167</v>
@@ -6891,13 +6920,13 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>16</v>
@@ -6911,7 +6940,7 @@
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6941,7 +6970,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6956,12 +6985,12 @@
         <v>178</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6976,7 +7005,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6988,7 +7017,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>103</v>
@@ -6996,7 +7025,7 @@
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>311</v>
+        <v>256</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -7011,7 +7040,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -7020,10 +7049,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>135</v>
@@ -7031,7 +7060,7 @@
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -7046,22 +7075,22 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -7081,7 +7110,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -7090,7 +7119,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c t="s" r="I156" s="7">
         <v>108</v>
@@ -7101,7 +7130,7 @@
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -7116,13 +7145,13 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>16</v>
@@ -7136,7 +7165,7 @@
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -7166,7 +7195,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -7178,7 +7207,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>18</v>
@@ -7186,7 +7215,7 @@
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -7201,7 +7230,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7210,7 +7239,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="I160" s="7">
         <v>219</v>
@@ -7221,7 +7250,7 @@
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7236,13 +7265,13 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>34</v>
@@ -7251,12 +7280,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -7271,7 +7300,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7283,14 +7312,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
-      <c r="M162" s="7"/>
+      <c t="s" r="M162" s="7">
+        <v>334</v>
+      </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
       <c r="A163" s="6"/>
@@ -7319,7 +7350,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7334,12 +7365,12 @@
         <v>179</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7354,7 +7385,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7366,15 +7397,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7389,7 +7420,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7404,14 +7435,14 @@
         <v>134</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c t="s" r="K166" s="7">
         <v>147</v>
       </c>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7426,7 +7457,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7435,18 +7466,18 @@
         <v>110</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -7461,13 +7492,13 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>110</v>
@@ -7481,7 +7512,7 @@
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7496,7 +7527,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7508,15 +7539,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7531,7 +7562,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7546,14 +7577,14 @@
         <v>37</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c t="s" r="K170" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7568,7 +7599,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7583,14 +7614,14 @@
         <v>190</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c t="s" r="K171" s="7">
         <v>60</v>
       </c>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7605,7 +7636,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7620,14 +7651,14 @@
         <v>44</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c t="s" r="K172" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>45</v>
+        <v>280</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7657,7 +7688,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7672,12 +7703,12 @@
         <v>127</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7692,7 +7723,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7707,12 +7738,12 @@
         <v>142</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7727,7 +7758,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7736,7 +7767,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c t="s" r="I176" s="7">
         <v>144</v>
@@ -7747,7 +7778,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7762,13 +7793,13 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>16</v>
@@ -7782,7 +7813,7 @@
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7797,7 +7828,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7806,7 +7837,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="I178" s="7">
         <v>93</v>
@@ -7817,7 +7848,7 @@
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7832,19 +7863,19 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>59</v>
@@ -7852,7 +7883,7 @@
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7867,7 +7898,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7879,17 +7910,17 @@
         <v>34</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>81</v>
       </c>
       <c t="s" r="K180" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>141</v>
+        <v>363</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7919,7 +7950,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7931,15 +7962,15 @@
         <v>110</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7947,14 +7978,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B183" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7969,7 +8000,7 @@
         <v>195</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c t="s" r="K183" s="7">
         <v>195</v>
@@ -7991,7 +8022,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -8003,17 +8034,17 @@
         <v>68</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c t="s" r="K184" s="7">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -8028,7 +8059,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -8040,17 +8071,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>88</v>
       </c>
       <c t="s" r="K185" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -8065,7 +8096,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -8077,7 +8108,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>19</v>
@@ -8085,7 +8116,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -8100,7 +8131,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -8112,15 +8143,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -8150,7 +8181,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8159,7 +8190,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>103</v>
@@ -8170,7 +8201,7 @@
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -8185,13 +8216,13 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>34</v>
@@ -8207,7 +8238,7 @@
       </c>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -8222,7 +8253,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8231,20 +8262,20 @@
         <v>34</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c t="s" r="K191" s="7">
         <v>35</v>
       </c>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8259,29 +8290,29 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c t="s" r="K192" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8311,7 +8342,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8323,7 +8354,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>162</v>
@@ -8331,7 +8362,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -8346,7 +8377,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8358,15 +8389,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8381,7 +8412,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8390,7 +8421,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="I196" s="7">
         <v>195</v>
@@ -8399,11 +8430,11 @@
         <v>184</v>
       </c>
       <c t="s" r="K196" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8418,13 +8449,13 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>34</v>
@@ -8440,7 +8471,7 @@
       </c>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8455,7 +8486,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8475,7 +8506,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8490,7 +8521,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8502,7 +8533,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>38</v>
@@ -8510,7 +8541,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8525,7 +8556,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8540,11 +8571,13 @@
         <v>113</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
-      <c r="M200" s="7"/>
+      <c t="s" r="M200" s="7">
+        <v>391</v>
+      </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
       <c t="s" r="A201" s="6">
@@ -8558,7 +8591,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8570,10 +8603,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>387</v>
+        <v>255</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -8606,7 +8639,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8618,15 +8651,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8641,7 +8674,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8653,15 +8686,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8676,7 +8709,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8688,7 +8721,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>118</v>
@@ -8696,7 +8729,7 @@
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8711,7 +8744,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8720,7 +8753,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c t="s" r="I206" s="7">
         <v>88</v>
@@ -8731,7 +8764,7 @@
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8746,19 +8779,19 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c t="s" r="H207" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>210</v>
@@ -8766,7 +8799,7 @@
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8781,7 +8814,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8790,18 +8823,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8816,27 +8849,27 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8866,7 +8899,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8886,7 +8919,7 @@
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8901,7 +8934,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8913,10 +8946,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8936,7 +8969,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8956,7 +8989,7 @@
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8971,7 +9004,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8983,7 +9016,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>38</v>
@@ -8991,7 +9024,7 @@
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -9021,7 +9054,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -9030,10 +9063,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>146</v>
@@ -9041,7 +9074,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -9056,27 +9089,27 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -9091,7 +9124,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -9100,18 +9133,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c t="s" r="I218" s="7">
         <v>168</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -9126,27 +9159,27 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -9161,7 +9194,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9170,20 +9203,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c t="s" r="K220" s="7">
         <v>193</v>
       </c>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9198,29 +9231,29 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c t="s" r="K221" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9250,7 +9283,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9259,10 +9292,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>208</v>
@@ -9270,7 +9303,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -9285,13 +9318,13 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>34</v>
@@ -9300,12 +9333,12 @@
         <v>53</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -9320,7 +9353,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9329,10 +9362,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>153</v>
@@ -9355,13 +9388,13 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>34</v>
@@ -9370,12 +9403,12 @@
         <v>155</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9390,7 +9423,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9405,7 +9438,7 @@
         <v>176</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -9438,19 +9471,19 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>72</v>
@@ -9458,7 +9491,7 @@
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9473,7 +9506,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9482,7 +9515,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c t="s" r="I230" s="7">
         <v>169</v>
@@ -9493,7 +9526,7 @@
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9508,22 +9541,22 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -9556,7 +9589,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9568,7 +9601,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>118</v>
@@ -9591,7 +9624,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9600,18 +9633,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c t="s" r="I234" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9626,19 +9659,19 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>190</v>
@@ -9646,7 +9679,7 @@
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9661,7 +9694,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9709,7 +9742,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9729,7 +9762,7 @@
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9744,7 +9777,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9759,14 +9792,14 @@
         <v>168</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c t="s" r="K239" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9781,7 +9814,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9793,13 +9826,13 @@
         <v>34</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>156</v>
       </c>
       <c t="s" r="K240" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
@@ -9833,7 +9866,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9842,18 +9875,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9868,27 +9901,27 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9903,7 +9936,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9915,7 +9948,7 @@
         <v>84</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>76</v>
@@ -9938,7 +9971,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9953,12 +9986,12 @@
         <v>169</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9988,7 +10021,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="F247" s="7">
         <v>320</v>
@@ -9997,10 +10030,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>214</v>
@@ -10023,19 +10056,19 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="F248" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>27</v>
@@ -10043,7 +10076,7 @@
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -10058,7 +10091,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="F249" s="7">
         <v>320</v>
@@ -10073,7 +10106,7 @@
         <v>163</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>311</v>
+        <v>256</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -10093,7 +10126,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="F250" s="7">
         <v>320</v>
@@ -10105,15 +10138,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -10128,7 +10161,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="F251" s="7">
         <v>320</v>
@@ -10137,18 +10170,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c t="s" r="I251" s="7">
         <v>72</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -10163,13 +10196,13 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="F252" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>16</v>
@@ -10183,7 +10216,7 @@
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -10198,7 +10231,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -10207,18 +10240,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c t="s" r="I253" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10233,13 +10266,13 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>16</v>
@@ -10253,7 +10286,7 @@
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10283,7 +10316,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -10295,15 +10328,15 @@
         <v>110</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10318,7 +10351,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -10330,7 +10363,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c t="s" r="J257" s="7">
         <v>184</v>
@@ -10338,7 +10371,7 @@
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10353,7 +10386,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10373,7 +10406,7 @@
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10388,7 +10421,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -10397,18 +10430,18 @@
         <v>110</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10423,22 +10456,22 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -10473,7 +10506,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10485,15 +10518,15 @@
         <v>84</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10508,7 +10541,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10523,12 +10556,12 @@
         <v>52</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10543,7 +10576,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10552,10 +10585,10 @@
         <v>110</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>210</v>
@@ -10563,7 +10596,7 @@
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10578,19 +10611,19 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>38</v>
@@ -10598,7 +10631,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10613,7 +10646,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10622,7 +10655,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c t="s" r="I266" s="7">
         <v>62</v>
@@ -10661,7 +10694,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -10676,12 +10709,12 @@
         <v>117</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10696,7 +10729,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -10708,7 +10741,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>55</v>
@@ -10731,7 +10764,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -10740,7 +10773,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c t="s" r="I270" s="7">
         <v>209</v>
@@ -10751,7 +10784,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10766,13 +10799,13 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>34</v>
@@ -10786,7 +10819,7 @@
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10801,7 +10834,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -10810,18 +10843,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>203</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10836,26 +10869,28 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
-      <c r="M273" s="7"/>
+      <c t="s" r="M273" s="7">
+        <v>474</v>
+      </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
       <c r="A274" s="6"/>
@@ -10884,7 +10919,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10893,18 +10928,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c t="s" r="I275" s="7">
         <v>66</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10919,13 +10954,13 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>34</v>
@@ -10939,7 +10974,7 @@
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10954,7 +10989,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10974,7 +11009,7 @@
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -10989,7 +11024,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -11001,7 +11036,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>198</v>
@@ -11009,7 +11044,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -11024,7 +11059,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -11039,14 +11074,14 @@
         <v>200</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="K279" s="7">
         <v>91</v>
       </c>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -11076,7 +11111,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -11091,12 +11126,12 @@
         <v>63</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -11111,7 +11146,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -11123,15 +11158,15 @@
         <v>84</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -11146,7 +11181,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -11158,7 +11193,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>208</v>
@@ -11181,7 +11216,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -11193,15 +11228,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -11216,7 +11251,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -11236,7 +11271,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -11251,7 +11286,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -11271,7 +11306,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11286,7 +11321,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -11306,7 +11341,7 @@
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -11321,7 +11356,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -11341,7 +11376,7 @@
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>479</v>
+        <v>362</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -11371,7 +11406,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11391,7 +11426,7 @@
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11406,7 +11441,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11421,12 +11456,12 @@
         <v>152</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11441,7 +11476,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11456,12 +11491,12 @@
         <v>59</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11491,7 +11526,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -11500,10 +11535,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>52</v>
@@ -11511,7 +11546,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11526,19 +11561,19 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>86</v>
@@ -11546,7 +11581,7 @@
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11561,7 +11596,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11570,7 +11605,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="I296" s="7">
         <v>137</v>
@@ -11581,7 +11616,7 @@
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11596,27 +11631,27 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11631,7 +11666,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11640,7 +11675,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c t="s" r="I298" s="7">
         <v>92</v>
@@ -11666,13 +11701,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>16</v>
@@ -11714,7 +11749,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11726,7 +11761,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>184</v>
@@ -11734,7 +11769,7 @@
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11749,7 +11784,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11761,7 +11796,7 @@
         <v>65</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>32</v>
@@ -11784,7 +11819,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11799,11 +11834,13 @@
         <v>193</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
-      <c r="M303" s="7"/>
+      <c t="s" r="M303" s="7">
+        <v>497</v>
+      </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
       <c r="A304" s="6"/>
@@ -11832,7 +11869,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -11852,7 +11889,7 @@
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11867,7 +11904,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11876,13 +11913,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c t="s" r="K306" s="7">
         <v>208</v>
@@ -11904,13 +11941,13 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>16</v>
@@ -11919,14 +11956,14 @@
         <v>70</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="K307" s="7">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11941,7 +11978,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11956,12 +11993,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11976,7 +12013,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11988,7 +12025,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>96</v>
@@ -12026,7 +12063,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -12038,7 +12075,7 @@
         <v>213</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>117</v>
@@ -12046,7 +12083,7 @@
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>496</v>
+        <v>502</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -12061,7 +12098,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -12076,12 +12113,12 @@
         <v>183</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -12096,7 +12133,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -12108,7 +12145,7 @@
         <v>84</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>106</v>
@@ -12116,7 +12153,7 @@
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>498</v>
+        <v>504</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -12131,7 +12168,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -12151,7 +12188,7 @@
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -12166,7 +12203,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -12178,15 +12215,15 @@
         <v>180</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12201,7 +12238,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -12213,15 +12250,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>500</v>
+        <v>506</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12236,7 +12273,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -12245,10 +12282,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>414</v>
+        <v>508</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>217</v>
@@ -12284,7 +12321,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -12296,7 +12333,7 @@
         <v>65</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>130</v>
@@ -12319,7 +12356,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -12331,15 +12368,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>505</v>
+        <v>512</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12354,7 +12391,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -12363,7 +12400,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>144</v>
@@ -12376,7 +12413,7 @@
       </c>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>506</v>
+        <v>513</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -12391,13 +12428,13 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>34</v>
@@ -12409,11 +12446,11 @@
         <v>88</v>
       </c>
       <c t="s" r="K322" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>507</v>
+        <v>514</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12428,7 +12465,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12437,7 +12474,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="I323" s="7">
         <v>76</v>
@@ -12448,7 +12485,7 @@
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12463,27 +12500,27 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>509</v>
+        <v>516</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12498,7 +12535,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12507,18 +12544,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>511</v>
+        <v>518</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12533,22 +12570,22 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -12581,7 +12618,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -12593,15 +12630,15 @@
         <v>68</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>515</v>
+        <v>522</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12616,7 +12653,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12631,12 +12668,12 @@
         <v>142</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>517</v>
+        <v>524</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12651,7 +12688,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12660,13 +12697,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c t="s" r="I330" s="7">
         <v>86</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -12686,19 +12723,19 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>169</v>
@@ -12706,7 +12743,7 @@
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>518</v>
+        <v>525</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12721,7 +12758,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12733,7 +12770,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>20</v>
@@ -12741,7 +12778,7 @@
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>519</v>
+        <v>526</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12756,7 +12793,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12768,15 +12805,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>520</v>
+        <v>527</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12802,11 +12839,11 @@
         <v>9854</v>
       </c>
       <c t="s" r="C335" s="7">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12828,7 +12865,7 @@
       </c>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>523</v>
+        <v>530</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12858,7 +12895,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12873,12 +12910,12 @@
         <v>127</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>525</v>
+        <v>532</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12893,7 +12930,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12908,12 +12945,12 @@
         <v>163</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>526</v>
+        <v>533</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12928,7 +12965,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12940,17 +12977,17 @@
         <v>65</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>118</v>
       </c>
       <c t="s" r="K339" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12965,7 +13002,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12983,11 +13020,11 @@
         <v>76</v>
       </c>
       <c t="s" r="K340" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -13002,7 +13039,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -13017,14 +13054,14 @@
         <v>93</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="K341" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>528</v>
+        <v>535</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -13039,7 +13076,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -13054,14 +13091,14 @@
         <v>36</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c t="s" r="K342" s="7">
         <v>123</v>
       </c>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -13091,7 +13128,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -13111,7 +13148,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>531</v>
+        <v>538</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -13126,7 +13163,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -13135,18 +13172,18 @@
         <v>110</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c t="s" r="I345" s="7">
         <v>147</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>533</v>
+        <v>540</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -13161,13 +13198,13 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>110</v>
@@ -13181,7 +13218,7 @@
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>534</v>
+        <v>541</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -13196,7 +13233,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -13205,10 +13242,10 @@
         <v>110</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>96</v>
@@ -13231,19 +13268,19 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>224</v>
@@ -13251,7 +13288,7 @@
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -13281,7 +13318,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -13293,15 +13330,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13316,7 +13353,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -13325,7 +13362,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="I351" s="7">
         <v>86</v>
@@ -13336,7 +13373,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>539</v>
+        <v>546</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13351,13 +13388,13 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>34</v>
@@ -13386,7 +13423,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -13401,14 +13438,14 @@
         <v>220</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c t="s" r="K353" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>540</v>
+        <v>547</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13423,7 +13460,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -13438,14 +13475,14 @@
         <v>59</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c t="s" r="K354" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13475,7 +13512,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -13487,10 +13524,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -13510,7 +13547,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13519,18 +13556,18 @@
         <v>68</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c t="s" r="I357" s="7">
         <v>154</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13545,13 +13582,13 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>68</v>
@@ -13560,7 +13597,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -13595,7 +13632,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13615,7 +13652,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13630,7 +13667,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13642,7 +13679,7 @@
         <v>180</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>147</v>
@@ -13650,7 +13687,7 @@
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>544</v>
+        <v>551</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13665,7 +13702,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13685,7 +13722,7 @@
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>545</v>
+        <v>552</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13700,7 +13737,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13709,18 +13746,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c t="s" r="I363" s="7">
         <v>152</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>546</v>
+        <v>553</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13735,13 +13772,13 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>34</v>
@@ -13750,12 +13787,12 @@
         <v>201</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13770,7 +13807,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13785,12 +13822,12 @@
         <v>39</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>547</v>
+        <v>554</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13820,7 +13857,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13840,7 +13877,7 @@
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13855,7 +13892,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13870,12 +13907,12 @@
         <v>138</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13890,7 +13927,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13905,14 +13942,14 @@
         <v>153</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c t="s" r="K369" s="7">
         <v>36</v>
       </c>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>549</v>
+        <v>556</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13927,7 +13964,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13947,7 +13984,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>550</v>
+        <v>557</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13977,7 +14014,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13986,18 +14023,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>552</v>
+        <v>559</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -14012,13 +14049,13 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>16</v>
@@ -14032,7 +14069,7 @@
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -14047,7 +14084,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -14059,7 +14096,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>138</v>
@@ -14067,7 +14104,7 @@
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>553</v>
+        <v>560</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -14082,7 +14119,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -14094,15 +14131,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>554</v>
+        <v>561</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -14117,7 +14154,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -14129,17 +14166,17 @@
         <v>180</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c t="s" r="K376" s="7">
         <v>37</v>
       </c>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>555</v>
+        <v>562</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -14154,7 +14191,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -14169,14 +14206,14 @@
         <v>19</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c t="s" r="K377" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -14206,7 +14243,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -14221,12 +14258,12 @@
         <v>178</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>558</v>
+        <v>565</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14241,7 +14278,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -14256,12 +14293,12 @@
         <v>101</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -14276,7 +14313,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -14288,7 +14325,7 @@
         <v>84</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>199</v>
@@ -14296,7 +14333,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14311,7 +14348,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -14326,10 +14363,10 @@
         <v>108</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="K382" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
@@ -14363,7 +14400,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14375,7 +14412,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>149</v>
@@ -14383,7 +14420,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>561</v>
+        <v>568</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14398,7 +14435,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14413,7 +14450,7 @@
         <v>209</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -14433,7 +14470,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -14442,18 +14479,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c t="s" r="I386" s="7">
         <v>156</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>564</v>
+        <v>571</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14468,22 +14505,22 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -14516,7 +14553,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -14525,7 +14562,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="I389" s="7">
         <v>85</v>
@@ -14551,13 +14588,13 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>16</v>
@@ -14566,12 +14603,12 @@
         <v>183</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>567</v>
+        <v>574</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14586,7 +14623,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -14595,13 +14632,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c t="s" r="I391" s="7">
         <v>217</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c t="s" r="K391" s="7">
         <v>208</v>
@@ -14623,13 +14660,13 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>16</v>
@@ -14638,14 +14675,14 @@
         <v>118</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c t="s" r="K392" s="7">
         <v>138</v>
       </c>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>518</v>
+        <v>525</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14660,7 +14697,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14669,7 +14706,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>91</v>
@@ -14678,11 +14715,11 @@
         <v>153</v>
       </c>
       <c t="s" r="K393" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>568</v>
+        <v>575</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14697,29 +14734,29 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>20</v>
       </c>
       <c t="s" r="K394" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14749,7 +14786,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
@@ -14771,7 +14808,7 @@
       </c>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14786,7 +14823,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="F397" s="7">
         <v>330</v>
@@ -14801,14 +14838,14 @@
         <v>224</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c t="s" r="K397" s="7">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14838,19 +14875,19 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>200</v>
@@ -14858,7 +14895,7 @@
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14884,11 +14921,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C401" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
@@ -14897,10 +14934,10 @@
         <v>65</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>55</v>
@@ -14908,7 +14945,7 @@
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14919,17 +14956,17 @@
         <v>5806</v>
       </c>
       <c t="s" r="C402" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>65</v>
@@ -14938,7 +14975,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -14973,7 +15010,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -14985,7 +15022,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>67</v>
@@ -15008,7 +15045,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -15028,7 +15065,7 @@
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>582</v>
+        <v>589</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -15043,7 +15080,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -15058,12 +15095,12 @@
         <v>169</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>583</v>
+        <v>590</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -15078,7 +15115,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -15087,18 +15124,18 @@
         <v>65</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c t="s" r="I407" s="7">
         <v>123</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>585</v>
+        <v>592</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -15128,7 +15165,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
@@ -15137,18 +15174,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -15163,19 +15200,19 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>178</v>
@@ -15183,7 +15220,7 @@
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>588</v>
+        <v>595</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -15213,7 +15250,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -15225,7 +15262,7 @@
         <v>65</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>127</v>
@@ -15233,7 +15270,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>590</v>
+        <v>597</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15248,7 +15285,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -15257,7 +15294,7 @@
         <v>65</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>142</v>
@@ -15268,7 +15305,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15283,27 +15320,27 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>65</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>592</v>
+        <v>599</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -15333,7 +15370,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -15342,7 +15379,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c t="s" r="I416" s="7">
         <v>86</v>
@@ -15368,13 +15405,13 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>16</v>
@@ -15383,17 +15420,17 @@
         <v>43</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>596</v>
+        <v>603</v>
       </c>
     </row>
     <row r="418" ht="15.75" customHeight="1">
       <c t="s" r="A418" s="9">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="B418" s="9"/>
       <c r="C418" s="9"/>
@@ -15413,7 +15450,7 @@
     <row r="419" ht="65.25" customHeight="1"/>
     <row r="420" ht="17.25" customHeight="1">
       <c t="s" r="A420" s="10">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="B420" s="10"/>
       <c r="C420" s="10"/>
@@ -15426,7 +15463,7 @@
       <c r="J420" s="10"/>
       <c r="K420" s="10"/>
       <c t="s" r="L420" s="11">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="M420" s="11"/>
       <c r="N420" s="11"/>
